--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DF5E2E-48AF-4B8E-8936-D87BEDB739A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1245DE50-4840-48C4-B670-2CE25BCF9A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,6 +194,38 @@
   </si>
   <si>
     <t>48300006:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20001,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20002,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20003,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20004,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20005,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20006,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20007,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20008,30001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -527,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
@@ -962,7 +994,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -973,8 +1005,8 @@
       <c r="H16" t="s">
         <v>28</v>
       </c>
-      <c r="I16">
-        <v>10001</v>
+      <c r="I16" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -999,8 +1031,8 @@
       <c r="H17" t="s">
         <v>28</v>
       </c>
-      <c r="I17">
-        <v>10001</v>
+      <c r="I17" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1011,7 +1043,7 @@
         <v>101</v>
       </c>
       <c r="C18">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <v>32</v>
@@ -1025,8 +1057,8 @@
       <c r="H18" t="s">
         <v>28</v>
       </c>
-      <c r="I18">
-        <v>10001</v>
+      <c r="I18" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1037,7 +1069,7 @@
         <v>101</v>
       </c>
       <c r="C19">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>45</v>
@@ -1051,8 +1083,8 @@
       <c r="H19" t="s">
         <v>28</v>
       </c>
-      <c r="I19">
-        <v>10001</v>
+      <c r="I19" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1063,10 +1095,10 @@
         <v>101</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D20">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1077,8 +1109,86 @@
       <c r="H20" t="s">
         <v>28</v>
       </c>
-      <c r="I20">
-        <v>10001</v>
+      <c r="I20" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>10106</v>
+      </c>
+      <c r="B21">
+        <v>101</v>
+      </c>
+      <c r="C21">
+        <v>79</v>
+      </c>
+      <c r="D21">
+        <v>350</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>10000</v>
+      </c>
+      <c r="H21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>10107</v>
+      </c>
+      <c r="B22">
+        <v>101</v>
+      </c>
+      <c r="C22">
+        <v>351</v>
+      </c>
+      <c r="D22">
+        <v>700</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>10000</v>
+      </c>
+      <c r="H22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>10108</v>
+      </c>
+      <c r="B23">
+        <v>101</v>
+      </c>
+      <c r="C23">
+        <v>701</v>
+      </c>
+      <c r="D23">
+        <v>1100</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>10000</v>
+      </c>
+      <c r="H23" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1245DE50-4840-48C4-B670-2CE25BCF9A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="18350" windowHeight="6880"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -20,9 +14,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,219 +30,326 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
   <si>
     <t>paipaiworld_config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_C</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:LONG&gt;_C</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_C</t>
   </si>
   <si>
     <t>order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_id</t>
+  </si>
+  <si>
+    <t>in_barries_kill_min</t>
+  </si>
+  <si>
+    <t>in_barries_kill_max</t>
+  </si>
+  <si>
+    <t>drop_ratio_min</t>
+  </si>
+  <si>
+    <t>drop_ratio_max</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>drop_items</t>
+  </si>
+  <si>
+    <t>drop_condition</t>
   </si>
   <si>
     <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落几率万分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>掉落物品：数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落条件id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_items</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_condition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:LONG&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>30%血掉血瓶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300001:1</t>
+  </si>
+  <si>
+    <t>10001,20001</t>
   </si>
   <si>
     <t>掉3个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:3</t>
   </si>
   <si>
     <t>掉2个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:2</t>
   </si>
   <si>
     <t>掉1个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>48200001:1</t>
   </si>
   <si>
-    <t>48300001:1</t>
+    <t>掉技能2</t>
   </si>
   <si>
     <t>48300002:1</t>
   </si>
   <si>
+    <t>掉技能3</t>
+  </si>
+  <si>
     <t>48300003:1</t>
   </si>
   <si>
+    <t>掉技能4</t>
+  </si>
+  <si>
     <t>48300004:1</t>
   </si>
   <si>
+    <t>掉技能5</t>
+  </si>
+  <si>
     <t>48300005:1</t>
   </si>
   <si>
-    <t>48200001:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48200001:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能3</t>
-  </si>
-  <si>
-    <t>掉技能4</t>
-  </si>
-  <si>
-    <t>掉技能5</t>
-  </si>
-  <si>
     <t>掉技能6</t>
   </si>
   <si>
-    <t>10001,20001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>48300006:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20001,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20002,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20003,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20004,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20005,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20006,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20007,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20008,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,12 +358,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.149998474074526"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -271,26 +557,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -339,7 +912,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -374,7 +947,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -548,123 +1121,118 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.625" customWidth="1"/>
+    <col min="2" max="2" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+    <col min="4" max="4" width="16.75" customWidth="1"/>
+    <col min="5" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="18.75" customWidth="1"/>
+    <col min="9" max="9" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>1</v>
       </c>
@@ -687,13 +1255,13 @@
         <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>2</v>
       </c>
@@ -716,13 +1284,13 @@
         <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>3</v>
       </c>
@@ -745,13 +1313,13 @@
         <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>4</v>
       </c>
@@ -771,16 +1339,16 @@
         <v>1000</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>5</v>
       </c>
@@ -800,16 +1368,16 @@
         <v>4000</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>6</v>
       </c>
@@ -829,16 +1397,16 @@
         <v>10000</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>7</v>
       </c>
@@ -858,16 +1426,16 @@
         <v>10000</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>8</v>
       </c>
@@ -887,16 +1455,16 @@
         <v>10000</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>9</v>
       </c>
@@ -916,16 +1484,16 @@
         <v>10000</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
         <v>37</v>
       </c>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>10</v>
       </c>
@@ -948,13 +1516,13 @@
         <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>11</v>
       </c>
@@ -974,7 +1542,7 @@
         <v>10000</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H15" t="s">
         <v>41</v>
@@ -983,7 +1551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>10101</v>
       </c>
@@ -1003,13 +1571,13 @@
         <v>10000</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>10102</v>
       </c>
@@ -1029,13 +1597,13 @@
         <v>10000</v>
       </c>
       <c r="H17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>10103</v>
       </c>
@@ -1055,13 +1623,13 @@
         <v>10000</v>
       </c>
       <c r="H18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>10104</v>
       </c>
@@ -1081,13 +1649,13 @@
         <v>10000</v>
       </c>
       <c r="H19" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>10105</v>
       </c>
@@ -1107,13 +1675,13 @@
         <v>10000</v>
       </c>
       <c r="H20" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>10106</v>
       </c>
@@ -1133,13 +1701,13 @@
         <v>10000</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>10107</v>
       </c>
@@ -1159,13 +1727,13 @@
         <v>10000</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>10108</v>
       </c>
@@ -1185,14 +1753,14 @@
         <v>10000</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C28E7FB-5E75-4E63-BCE3-80E202A4C97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F8AA89-FDDA-4274-957E-AAA30994E988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1042,7 +1042,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1065,10 +1065,10 @@
         <v>101</v>
       </c>
       <c r="C17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1091,10 +1091,10 @@
         <v>101</v>
       </c>
       <c r="C18">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D18">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1117,10 +1117,10 @@
         <v>101</v>
       </c>
       <c r="C19">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D19">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1143,7 +1143,7 @@
         <v>101</v>
       </c>
       <c r="C20">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D20">
         <v>72</v>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F8AA89-FDDA-4274-957E-AAA30994E988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35DA827-F0A2-41F7-8962-0B5230C49221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -230,50 +230,6 @@
   </si>
   <si>
     <t>10001,20009,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20010,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20011,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20012,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20013,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20014,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20015,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20016,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20017,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20018,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20019,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20020,30001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1169,7 +1125,7 @@
         <v>101</v>
       </c>
       <c r="C21">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D21">
         <v>92</v>
@@ -1198,7 +1154,7 @@
         <v>93</v>
       </c>
       <c r="D22">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1221,10 +1177,10 @@
         <v>101</v>
       </c>
       <c r="C23">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D23">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1247,10 +1203,10 @@
         <v>101</v>
       </c>
       <c r="C24">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="D24">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1266,290 +1222,37 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>10110</v>
-      </c>
-      <c r="B25">
-        <v>101</v>
-      </c>
-      <c r="C25">
-        <v>188</v>
-      </c>
-      <c r="D25">
-        <v>220</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>10000</v>
-      </c>
-      <c r="H25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>10111</v>
-      </c>
-      <c r="B26">
-        <v>101</v>
-      </c>
-      <c r="C26">
-        <v>230</v>
-      </c>
-      <c r="D26">
-        <v>245</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>10000</v>
-      </c>
-      <c r="H26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>52</v>
-      </c>
+      <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>10112</v>
-      </c>
-      <c r="B27">
-        <v>101</v>
-      </c>
-      <c r="C27">
-        <v>246</v>
-      </c>
-      <c r="D27">
-        <v>275</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>10000</v>
-      </c>
-      <c r="H27" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>53</v>
-      </c>
+      <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>10113</v>
-      </c>
-      <c r="B28">
-        <v>101</v>
-      </c>
-      <c r="C28">
-        <v>276</v>
-      </c>
-      <c r="D28">
-        <v>315</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>10000</v>
-      </c>
-      <c r="H28" t="s">
-        <v>28</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>10114</v>
-      </c>
-      <c r="B29">
-        <v>101</v>
-      </c>
-      <c r="C29">
-        <v>316</v>
-      </c>
-      <c r="D29">
-        <v>365</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>10000</v>
-      </c>
-      <c r="H29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="I29" s="2"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>10115</v>
-      </c>
-      <c r="B30">
-        <v>101</v>
-      </c>
-      <c r="C30">
-        <v>366</v>
-      </c>
-      <c r="D30">
-        <v>425</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>10000</v>
-      </c>
-      <c r="H30" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="I30" s="2"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>10116</v>
-      </c>
-      <c r="B31">
-        <v>101</v>
-      </c>
-      <c r="C31">
-        <v>435</v>
-      </c>
-      <c r="D31">
-        <v>455</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>10000</v>
-      </c>
-      <c r="H31" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>10117</v>
-      </c>
-      <c r="B32">
-        <v>101</v>
-      </c>
-      <c r="C32">
-        <v>456</v>
-      </c>
-      <c r="D32">
-        <v>500</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>10000</v>
-      </c>
-      <c r="H32" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>10118</v>
-      </c>
-      <c r="B33">
-        <v>101</v>
-      </c>
-      <c r="C33">
-        <v>501</v>
-      </c>
-      <c r="D33">
-        <v>560</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>10000</v>
-      </c>
-      <c r="H33" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>10119</v>
-      </c>
-      <c r="B34">
-        <v>101</v>
-      </c>
-      <c r="C34">
-        <v>561</v>
-      </c>
-      <c r="D34">
-        <v>635</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>10000</v>
-      </c>
-      <c r="H34" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>10120</v>
-      </c>
-      <c r="B35">
-        <v>101</v>
-      </c>
-      <c r="C35">
-        <v>636</v>
-      </c>
-      <c r="D35">
-        <v>700</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>10000</v>
-      </c>
-      <c r="H35" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I35" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35DA827-F0A2-41F7-8962-0B5230C49221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F247F8-5085-449F-AA2D-D662B8D98346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -230,6 +230,14 @@
   </si>
   <si>
     <t>10001,20009,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20010,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20011,30001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1024,7 +1032,7 @@
         <v>12</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1047,10 +1055,10 @@
         <v>101</v>
       </c>
       <c r="C18">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1073,10 +1081,10 @@
         <v>101</v>
       </c>
       <c r="C19">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D19">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1099,10 +1107,10 @@
         <v>101</v>
       </c>
       <c r="C20">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D20">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1125,10 +1133,10 @@
         <v>101</v>
       </c>
       <c r="C21">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D21">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1151,10 +1159,10 @@
         <v>101</v>
       </c>
       <c r="C22">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D22">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1177,10 +1185,10 @@
         <v>101</v>
       </c>
       <c r="C23">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D23">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1203,10 +1211,10 @@
         <v>101</v>
       </c>
       <c r="C24">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D24">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1222,10 +1230,56 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I25" s="2"/>
+      <c r="A25">
+        <v>10110</v>
+      </c>
+      <c r="B25">
+        <v>101</v>
+      </c>
+      <c r="C25">
+        <v>133</v>
+      </c>
+      <c r="D25">
+        <v>151</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>10000</v>
+      </c>
+      <c r="H25" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I26" s="2"/>
+      <c r="A26">
+        <v>10111</v>
+      </c>
+      <c r="B26">
+        <v>101</v>
+      </c>
+      <c r="C26">
+        <v>152</v>
+      </c>
+      <c r="D26">
+        <v>172</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>10000</v>
+      </c>
+      <c r="H26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="I27" s="2"/>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F247F8-5085-449F-AA2D-D662B8D98346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="15580"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -20,9 +14,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,231 +30,353 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="58">
   <si>
     <t>paipaiworld_config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_C</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:LONG&gt;_C</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_C</t>
   </si>
   <si>
     <t>order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_id</t>
+  </si>
+  <si>
+    <t>in_barries_kill_min</t>
+  </si>
+  <si>
+    <t>in_barries_kill_max</t>
+  </si>
+  <si>
+    <t>drop_ratio_min</t>
+  </si>
+  <si>
+    <t>drop_ratio_max</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>drop_items</t>
+  </si>
+  <si>
+    <t>drop_condition</t>
   </si>
   <si>
     <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落几率万分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>掉落物品：数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落条件id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_items</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_condition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:LONG&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>30%血掉血瓶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300001:1</t>
+  </si>
+  <si>
+    <t>10001,20001</t>
   </si>
   <si>
     <t>掉3个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:3</t>
   </si>
   <si>
     <t>掉2个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:2</t>
   </si>
   <si>
     <t>掉1个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>48200001:1</t>
   </si>
   <si>
-    <t>48300001:1</t>
+    <t>掉技能2</t>
   </si>
   <si>
     <t>48300002:1</t>
   </si>
   <si>
+    <t>掉技能3</t>
+  </si>
+  <si>
     <t>48300003:1</t>
   </si>
   <si>
+    <t>掉技能4</t>
+  </si>
+  <si>
     <t>48300004:1</t>
   </si>
   <si>
+    <t>掉技能5</t>
+  </si>
+  <si>
     <t>48300005:1</t>
   </si>
   <si>
-    <t>48200001:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48200001:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能3</t>
-  </si>
-  <si>
-    <t>掉技能4</t>
-  </si>
-  <si>
-    <t>掉技能5</t>
-  </si>
-  <si>
     <t>掉技能6</t>
   </si>
   <si>
-    <t>10001,20001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>48300006:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20001,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20002,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20003,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20004,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20005,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20006,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20007,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20008,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20009,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20010,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20011,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20001,40001</t>
+  </si>
+  <si>
+    <t>10001,20002,40001</t>
+  </si>
+  <si>
+    <t>10001,20003,40001</t>
+  </si>
+  <si>
+    <t>10001,20004,40001</t>
+  </si>
+  <si>
+    <t>10001,20005,40001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,12 +385,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.149998474074526"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -283,26 +584,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -351,7 +939,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -386,7 +974,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -560,123 +1148,118 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.625" customWidth="1"/>
+    <col min="2" max="2" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+    <col min="4" max="4" width="16.75" customWidth="1"/>
+    <col min="5" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="18.75" customWidth="1"/>
+    <col min="9" max="9" width="19.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>1</v>
       </c>
@@ -699,13 +1282,13 @@
         <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>2</v>
       </c>
@@ -728,13 +1311,13 @@
         <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>3</v>
       </c>
@@ -757,13 +1340,13 @@
         <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>4</v>
       </c>
@@ -783,16 +1366,16 @@
         <v>1000</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>5</v>
       </c>
@@ -812,16 +1395,16 @@
         <v>4000</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>6</v>
       </c>
@@ -841,16 +1424,16 @@
         <v>10000</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>7</v>
       </c>
@@ -870,16 +1453,16 @@
         <v>10000</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>8</v>
       </c>
@@ -899,16 +1482,16 @@
         <v>10000</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>9</v>
       </c>
@@ -928,16 +1511,16 @@
         <v>10000</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
         <v>37</v>
       </c>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>10</v>
       </c>
@@ -960,13 +1543,13 @@
         <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>11</v>
       </c>
@@ -986,7 +1569,7 @@
         <v>10000</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H15" t="s">
         <v>41</v>
@@ -995,7 +1578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>10101</v>
       </c>
@@ -1015,13 +1598,13 @@
         <v>10000</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>10102</v>
       </c>
@@ -1041,13 +1624,13 @@
         <v>10000</v>
       </c>
       <c r="H17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>10103</v>
       </c>
@@ -1067,13 +1650,13 @@
         <v>10000</v>
       </c>
       <c r="H18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>10104</v>
       </c>
@@ -1093,13 +1676,13 @@
         <v>10000</v>
       </c>
       <c r="H19" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>10105</v>
       </c>
@@ -1119,13 +1702,13 @@
         <v>10000</v>
       </c>
       <c r="H20" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>10106</v>
       </c>
@@ -1145,13 +1728,13 @@
         <v>10000</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>10107</v>
       </c>
@@ -1171,13 +1754,13 @@
         <v>10000</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>10108</v>
       </c>
@@ -1197,13 +1780,13 @@
         <v>10000</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>10109</v>
       </c>
@@ -1223,13 +1806,13 @@
         <v>10000</v>
       </c>
       <c r="H24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>10110</v>
       </c>
@@ -1249,13 +1832,13 @@
         <v>10000</v>
       </c>
       <c r="H25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>10111</v>
       </c>
@@ -1275,41 +1858,179 @@
         <v>10000</v>
       </c>
       <c r="H26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9">
+      <c r="A27">
+        <v>10112</v>
+      </c>
+      <c r="B27">
+        <v>201</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>10000</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28">
+        <v>10113</v>
+      </c>
+      <c r="B28">
+        <v>201</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>7</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>10000</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29">
+        <v>10114</v>
+      </c>
+      <c r="B29">
+        <v>201</v>
+      </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>10000</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30">
+        <v>10115</v>
+      </c>
+      <c r="B30">
+        <v>201</v>
+      </c>
+      <c r="C30">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>15</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>10000</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31">
+        <v>10116</v>
+      </c>
+      <c r="B31">
+        <v>201</v>
+      </c>
+      <c r="C31">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <v>22</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>10000</v>
+      </c>
+      <c r="H31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32">
+        <v>10117</v>
+      </c>
+      <c r="B32">
+        <v>201</v>
+      </c>
+      <c r="C32">
+        <v>23</v>
+      </c>
+      <c r="D32">
+        <v>27</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>10000</v>
+      </c>
+      <c r="H32" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="9:9">
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="9:9">
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="9:9">
       <c r="I35" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15580"/>
+    <workbookView windowWidth="29100" windowHeight="14540"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="58">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -191,19 +191,19 @@
     <t>10001,20011,30001</t>
   </si>
   <si>
-    <t>10001,20001,40001</t>
-  </si>
-  <si>
-    <t>10001,20002,40001</t>
-  </si>
-  <si>
-    <t>10001,20003,40001</t>
-  </si>
-  <si>
-    <t>10001,20004,40001</t>
-  </si>
-  <si>
-    <t>10001,20005,40001</t>
+    <t>30001,20001,40001</t>
+  </si>
+  <si>
+    <t>30001,20002,40001</t>
+  </si>
+  <si>
+    <t>30001,20003,40001</t>
+  </si>
+  <si>
+    <t>30001,20004,40001</t>
+  </si>
+  <si>
+    <t>30001,20005,40001</t>
   </si>
 </sst>
 </file>
@@ -216,14 +216,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -685,148 +678,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1154,7 +1147,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
@@ -1872,7 +1865,7 @@
         <v>201</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -1979,7 +1972,7 @@
         <v>16</v>
       </c>
       <c r="D31">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1994,40 +1987,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32">
-        <v>10117</v>
-      </c>
-      <c r="B32">
-        <v>201</v>
-      </c>
-      <c r="C32">
-        <v>23</v>
-      </c>
-      <c r="D32">
-        <v>27</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>10000</v>
-      </c>
-      <c r="H32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>57</v>
-      </c>
+    <row r="32" spans="9:9">
+      <c r="I32" s="2"/>
     </row>
     <row r="33" spans="9:9">
       <c r="I33" s="2"/>
     </row>
     <row r="34" spans="9:9">
       <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="9:9">
-      <c r="I35" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>201</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1917,10 +1917,10 @@
         <v>201</v>
       </c>
       <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
         <v>8</v>
-      </c>
-      <c r="D29">
-        <v>10</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1943,10 +1943,10 @@
         <v>201</v>
       </c>
       <c r="C30">
+        <v>9</v>
+      </c>
+      <c r="D30">
         <v>11</v>
-      </c>
-      <c r="D30">
-        <v>15</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>201</v>
       </c>
       <c r="C31">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D31">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="E31">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35DA827-F0A2-41F7-8962-0B5230C49221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="29100" windowHeight="14540"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -20,9 +14,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,223 +30,346 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="58">
   <si>
     <t>paipaiworld_config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_C</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:LONG&gt;_C</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_C</t>
   </si>
   <si>
     <t>order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_id</t>
+  </si>
+  <si>
+    <t>in_barries_kill_min</t>
+  </si>
+  <si>
+    <t>in_barries_kill_max</t>
+  </si>
+  <si>
+    <t>drop_ratio_min</t>
+  </si>
+  <si>
+    <t>drop_ratio_max</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>drop_items</t>
+  </si>
+  <si>
+    <t>drop_condition</t>
   </si>
   <si>
     <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落几率万分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>掉落物品：数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落条件id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_items</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_condition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:LONG&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>30%血掉血瓶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300001:1</t>
+  </si>
+  <si>
+    <t>10001,20001</t>
   </si>
   <si>
     <t>掉3个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:3</t>
   </si>
   <si>
     <t>掉2个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:2</t>
   </si>
   <si>
     <t>掉1个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>48200001:1</t>
   </si>
   <si>
-    <t>48300001:1</t>
+    <t>掉技能2</t>
   </si>
   <si>
     <t>48300002:1</t>
   </si>
   <si>
+    <t>掉技能3</t>
+  </si>
+  <si>
     <t>48300003:1</t>
   </si>
   <si>
+    <t>掉技能4</t>
+  </si>
+  <si>
     <t>48300004:1</t>
   </si>
   <si>
+    <t>掉技能5</t>
+  </si>
+  <si>
     <t>48300005:1</t>
   </si>
   <si>
-    <t>48200001:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48200001:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能3</t>
-  </si>
-  <si>
-    <t>掉技能4</t>
-  </si>
-  <si>
-    <t>掉技能5</t>
-  </si>
-  <si>
     <t>掉技能6</t>
   </si>
   <si>
-    <t>10001,20001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>48300006:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20001,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20002,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20003,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20004,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20005,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20006,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20007,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20008,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20009,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20010,30001</t>
+  </si>
+  <si>
+    <t>10001,20011,30001</t>
+  </si>
+  <si>
+    <t>30001,20001,40001</t>
+  </si>
+  <si>
+    <t>30001,20002,40001</t>
+  </si>
+  <si>
+    <t>30001,20003,40001</t>
+  </si>
+  <si>
+    <t>30001,20004,40001</t>
+  </si>
+  <si>
+    <t>30001,20005,40001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,12 +378,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.149998474074526"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -275,26 +577,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -343,7 +932,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -378,7 +967,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -552,123 +1141,118 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.625" customWidth="1"/>
+    <col min="2" max="2" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+    <col min="4" max="4" width="16.75" customWidth="1"/>
+    <col min="5" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="18.75" customWidth="1"/>
+    <col min="9" max="9" width="19.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>1</v>
       </c>
@@ -691,13 +1275,13 @@
         <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>2</v>
       </c>
@@ -720,13 +1304,13 @@
         <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>3</v>
       </c>
@@ -749,13 +1333,13 @@
         <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>4</v>
       </c>
@@ -775,16 +1359,16 @@
         <v>1000</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>5</v>
       </c>
@@ -804,16 +1388,16 @@
         <v>4000</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>6</v>
       </c>
@@ -833,16 +1417,16 @@
         <v>10000</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>7</v>
       </c>
@@ -862,16 +1446,16 @@
         <v>10000</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>8</v>
       </c>
@@ -891,16 +1475,16 @@
         <v>10000</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>9</v>
       </c>
@@ -920,16 +1504,16 @@
         <v>10000</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
         <v>37</v>
       </c>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>10</v>
       </c>
@@ -952,13 +1536,13 @@
         <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>11</v>
       </c>
@@ -978,7 +1562,7 @@
         <v>10000</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H15" t="s">
         <v>41</v>
@@ -987,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>10101</v>
       </c>
@@ -1007,13 +1591,13 @@
         <v>10000</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>10102</v>
       </c>
@@ -1024,7 +1608,7 @@
         <v>12</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1033,13 +1617,13 @@
         <v>10000</v>
       </c>
       <c r="H17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>10103</v>
       </c>
@@ -1047,10 +1631,10 @@
         <v>101</v>
       </c>
       <c r="C18">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1059,13 +1643,13 @@
         <v>10000</v>
       </c>
       <c r="H18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>10104</v>
       </c>
@@ -1073,10 +1657,10 @@
         <v>101</v>
       </c>
       <c r="C19">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D19">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1085,13 +1669,13 @@
         <v>10000</v>
       </c>
       <c r="H19" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>10105</v>
       </c>
@@ -1099,10 +1683,10 @@
         <v>101</v>
       </c>
       <c r="C20">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D20">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1111,13 +1695,13 @@
         <v>10000</v>
       </c>
       <c r="H20" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>10106</v>
       </c>
@@ -1125,10 +1709,10 @@
         <v>101</v>
       </c>
       <c r="C21">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D21">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1137,13 +1721,13 @@
         <v>10000</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>10107</v>
       </c>
@@ -1151,10 +1735,10 @@
         <v>101</v>
       </c>
       <c r="C22">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D22">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1163,13 +1747,13 @@
         <v>10000</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>10108</v>
       </c>
@@ -1177,10 +1761,10 @@
         <v>101</v>
       </c>
       <c r="C23">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D23">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1189,13 +1773,13 @@
         <v>10000</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>10109</v>
       </c>
@@ -1203,59 +1787,217 @@
         <v>101</v>
       </c>
       <c r="C24">
+        <v>115</v>
+      </c>
+      <c r="D24">
+        <v>132</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>10000</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25">
+        <v>10110</v>
+      </c>
+      <c r="B25">
+        <v>101</v>
+      </c>
+      <c r="C25">
         <v>133</v>
       </c>
-      <c r="D24">
-        <v>153</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>10000</v>
-      </c>
-      <c r="H24" t="s">
-        <v>28</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D25">
+        <v>151</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>10000</v>
+      </c>
+      <c r="H25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26">
+        <v>10111</v>
+      </c>
+      <c r="B26">
+        <v>101</v>
+      </c>
+      <c r="C26">
+        <v>152</v>
+      </c>
+      <c r="D26">
+        <v>172</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>10000</v>
+      </c>
+      <c r="H26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27">
+        <v>10112</v>
+      </c>
+      <c r="B27">
+        <v>201</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>10000</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28">
+        <v>10113</v>
+      </c>
+      <c r="B28">
+        <v>201</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>10000</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29">
+        <v>10114</v>
+      </c>
+      <c r="B29">
+        <v>201</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>8</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>10000</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30">
+        <v>10115</v>
+      </c>
+      <c r="B30">
+        <v>201</v>
+      </c>
+      <c r="C30">
+        <v>9</v>
+      </c>
+      <c r="D30">
+        <v>11</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>10000</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31">
+        <v>10116</v>
+      </c>
+      <c r="B31">
+        <v>201</v>
+      </c>
+      <c r="C31">
+        <v>12</v>
+      </c>
+      <c r="D31">
+        <v>99</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>10000</v>
+      </c>
+      <c r="H31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="9:9">
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="9:9">
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="9:9">
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I35" s="2"/>
-    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F247F8-5085-449F-AA2D-D662B8D98346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387CC3AB-691B-4030-85E9-8E5B42D41218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_barires_drop_v8!$A$4:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_barires_drop_v8!$A$4:$I$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="48">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -131,114 +131,83 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>30%血掉血瓶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉3个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉2个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉1个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48200001:1</t>
-  </si>
-  <si>
     <t>48300001:1</t>
   </si>
   <si>
-    <t>48300002:1</t>
-  </si>
-  <si>
-    <t>48300003:1</t>
-  </si>
-  <si>
-    <t>48300004:1</t>
-  </si>
-  <si>
-    <t>48300005:1</t>
-  </si>
-  <si>
-    <t>48200001:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48200001:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能3</t>
-  </si>
-  <si>
-    <t>掉技能4</t>
-  </si>
-  <si>
-    <t>掉技能5</t>
-  </si>
-  <si>
-    <t>掉技能6</t>
-  </si>
-  <si>
-    <t>10001,20001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48300006:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20001,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20002,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20003,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20004,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20005,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20006,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20007,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20008,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20009,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20010,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20011,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>10001,20000,30001,40001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10002,20000,30001,40002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10003,20000,30001,40003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10004,20000,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20010,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20010,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20010,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20010,30001</t>
+  </si>
+  <si>
+    <t>10001,20020,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20020,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20020,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20020,30001</t>
+  </si>
+  <si>
+    <t>10001,20030,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20030,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20030,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20030,30001</t>
+  </si>
+  <si>
+    <t>10001,20040,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20040,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20040,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20040,30001</t>
+  </si>
+  <si>
+    <t>10001,20050,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20050,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20050,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20050,30001</t>
   </si>
 </sst>
 </file>
@@ -571,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
@@ -678,219 +647,198 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1</v>
+        <v>10001</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>10000</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>2</v>
+        <v>10002</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>10000</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>23</v>
+        <v>2000</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>3</v>
+        <v>10003</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>10000</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>23</v>
+        <v>4000</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>4</v>
+        <v>10004</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1000</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>24</v>
+        <v>10000</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>5</v>
+        <v>10005</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>4000</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>6</v>
+        <v>10006</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D10">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E10">
-        <v>4001</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>10000</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>26</v>
+        <v>2000</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>7</v>
+        <v>10007</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>10000</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>35</v>
+        <v>4000</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>8</v>
+        <v>10008</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -898,115 +846,103 @@
       <c r="F12">
         <v>10000</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="H12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>9</v>
+        <v>10009</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>10000</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>37</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>10</v>
+        <v>10010</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>10000</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>38</v>
+        <v>2000</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>11</v>
+        <v>10011</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>10000</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>39</v>
+        <v>4000</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>10101</v>
+        <v>10012</v>
       </c>
       <c r="B16">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1015,102 +951,102 @@
         <v>10000</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>10102</v>
+        <v>10013</v>
       </c>
       <c r="B17">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D17">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>10103</v>
+        <v>10014</v>
       </c>
       <c r="B18">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D18">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="H18" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>10104</v>
+        <v>10015</v>
       </c>
       <c r="B19">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C19">
         <v>37</v>
       </c>
       <c r="D19">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="H19" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>10105</v>
+        <v>10016</v>
       </c>
       <c r="B20">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D20">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1119,102 +1055,102 @@
         <v>10000</v>
       </c>
       <c r="H20" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>10106</v>
+        <v>10017</v>
       </c>
       <c r="B21">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D21">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>10107</v>
+        <v>10018</v>
       </c>
       <c r="B22">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D22">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>10108</v>
+        <v>10019</v>
       </c>
       <c r="B23">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="D23">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>10109</v>
+        <v>10020</v>
       </c>
       <c r="B24">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="D24">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1223,90 +1159,739 @@
         <v>10000</v>
       </c>
       <c r="H24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>10110</v>
+        <v>10021</v>
       </c>
       <c r="B25">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="D25">
-        <v>151</v>
+        <v>330</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>10111</v>
+        <v>10022</v>
       </c>
       <c r="B26">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="D26">
-        <v>172</v>
+        <v>330</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26">
+        <v>2000</v>
+      </c>
+      <c r="H26" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>10023</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>109</v>
+      </c>
+      <c r="D27">
+        <v>330</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>4000</v>
+      </c>
+      <c r="H27" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>10024</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>109</v>
+      </c>
+      <c r="D28">
+        <v>330</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
         <v>10000</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H28" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>20001</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>331</v>
+      </c>
+      <c r="D29">
+        <v>360</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>1000</v>
+      </c>
+      <c r="H29" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>20002</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30">
+        <v>331</v>
+      </c>
+      <c r="D30">
+        <v>360</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>2000</v>
+      </c>
+      <c r="H30" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>20003</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31">
+        <v>331</v>
+      </c>
+      <c r="D31">
+        <v>360</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>4000</v>
+      </c>
+      <c r="H31" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>20004</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32">
+        <v>331</v>
+      </c>
+      <c r="D32">
+        <v>360</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>10000</v>
+      </c>
+      <c r="H32" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>20005</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>361</v>
+      </c>
+      <c r="D33">
+        <v>400</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1000</v>
+      </c>
+      <c r="H33" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I35" s="2"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>20006</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>361</v>
+      </c>
+      <c r="D34">
+        <v>400</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>2000</v>
+      </c>
+      <c r="H34" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>20007</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>361</v>
+      </c>
+      <c r="D35">
+        <v>400</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>4000</v>
+      </c>
+      <c r="H35" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>20008</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36">
+        <v>361</v>
+      </c>
+      <c r="D36">
+        <v>400</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>10000</v>
+      </c>
+      <c r="H36" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>20009</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37">
+        <v>401</v>
+      </c>
+      <c r="D37">
+        <v>450</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>1000</v>
+      </c>
+      <c r="H37" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>20010</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>401</v>
+      </c>
+      <c r="D38">
+        <v>450</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>2000</v>
+      </c>
+      <c r="H38" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>20011</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <v>401</v>
+      </c>
+      <c r="D39">
+        <v>450</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>4000</v>
+      </c>
+      <c r="H39" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>20012</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+      <c r="C40">
+        <v>401</v>
+      </c>
+      <c r="D40">
+        <v>450</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>10000</v>
+      </c>
+      <c r="H40" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>20013</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>451</v>
+      </c>
+      <c r="D41">
+        <v>500</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>1000</v>
+      </c>
+      <c r="H41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>20014</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42">
+        <v>451</v>
+      </c>
+      <c r="D42">
+        <v>500</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>2000</v>
+      </c>
+      <c r="H42" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>20015</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43">
+        <v>451</v>
+      </c>
+      <c r="D43">
+        <v>500</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>4000</v>
+      </c>
+      <c r="H43" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>20016</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44">
+        <v>451</v>
+      </c>
+      <c r="D44">
+        <v>500</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>10000</v>
+      </c>
+      <c r="H44" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>20017</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>501</v>
+      </c>
+      <c r="D45">
+        <v>550</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>1000</v>
+      </c>
+      <c r="H45" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>20018</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <v>501</v>
+      </c>
+      <c r="D46">
+        <v>550</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>2000</v>
+      </c>
+      <c r="H46" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>20019</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>501</v>
+      </c>
+      <c r="D47">
+        <v>500</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>4000</v>
+      </c>
+      <c r="H47" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>20020</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48">
+        <v>501</v>
+      </c>
+      <c r="D48">
+        <v>550</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>10000</v>
+      </c>
+      <c r="H48" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>20021</v>
+      </c>
+      <c r="B49">
+        <v>2</v>
+      </c>
+      <c r="C49">
+        <v>551</v>
+      </c>
+      <c r="D49">
+        <v>600</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>1000</v>
+      </c>
+      <c r="H49" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>20022</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50">
+        <v>551</v>
+      </c>
+      <c r="D50">
+        <v>600</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>2000</v>
+      </c>
+      <c r="H50" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>20023</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <v>501</v>
+      </c>
+      <c r="D51">
+        <v>600</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>4000</v>
+      </c>
+      <c r="H51" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>20024</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <v>551</v>
+      </c>
+      <c r="D52">
+        <v>600</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>10000</v>
+      </c>
+      <c r="H52" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387CC3AB-691B-4030-85E9-8E5B42D41218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C371B08D-6B26-4ED2-BF9C-E3B65CB22AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -150,64 +150,73 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10001,20010,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20010,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20010,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20010,30001</t>
-  </si>
-  <si>
-    <t>10001,20020,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20020,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20020,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20020,30001</t>
-  </si>
-  <si>
-    <t>10001,20030,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20030,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20030,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20030,30001</t>
-  </si>
-  <si>
-    <t>10001,20040,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20040,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20040,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20040,30001</t>
-  </si>
-  <si>
-    <t>10001,20050,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20050,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20050,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20050,30001</t>
+    <t>10001,20001,30001,40001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10002,20001,30001,40002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10003,20001,30001,40003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10004,20001,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20002,30001,40001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10002,20002,30001,40002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10003,20002,30001,40003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10004,20002,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10004,20004,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20004,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20004,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20004,30001,40003</t>
+  </si>
+  <si>
+    <t>10001,20003,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20003,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20003,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20003,30001</t>
+  </si>
+  <si>
+    <t>10001,20005,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20005,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20005,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20005,30001</t>
   </si>
 </sst>
 </file>
@@ -980,7 +989,7 @@
         <v>23</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1006,7 +1015,7 @@
         <v>23</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1032,7 +1041,7 @@
         <v>23</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1058,7 +1067,7 @@
         <v>23</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
@@ -1084,7 +1093,7 @@
         <v>23</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
@@ -1110,7 +1119,7 @@
         <v>23</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
@@ -1136,7 +1145,7 @@
         <v>23</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
@@ -1162,7 +1171,7 @@
         <v>23</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
@@ -1604,7 +1613,7 @@
         <v>23</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
@@ -1630,7 +1639,7 @@
         <v>23</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
@@ -1656,7 +1665,7 @@
         <v>23</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
@@ -1682,7 +1691,7 @@
         <v>23</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
@@ -1708,7 +1717,7 @@
         <v>23</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
@@ -1734,7 +1743,7 @@
         <v>23</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
@@ -1760,7 +1769,7 @@
         <v>23</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
@@ -1786,7 +1795,7 @@
         <v>23</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C371B08D-6B26-4ED2-BF9C-E3B65CB22AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -20,9 +14,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,209 +30,326 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="49">
   <si>
     <t>paipaiworld_config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_C</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:LONG&gt;_C</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_C</t>
   </si>
   <si>
     <t>order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_id</t>
+  </si>
+  <si>
+    <t>in_barries_kill_min</t>
+  </si>
+  <si>
+    <t>in_barries_kill_max</t>
+  </si>
+  <si>
+    <t>drop_ratio_min</t>
+  </si>
+  <si>
+    <t>drop_ratio_max</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>drop_items</t>
+  </si>
+  <si>
+    <t>drop_condition</t>
   </si>
   <si>
     <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落几率万分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>掉落物品：数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落条件id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_items</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_condition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:LONG&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>48300001:1</t>
   </si>
   <si>
+    <t>20000,30001</t>
+  </si>
+  <si>
+    <t>10002,20000,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20000,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20000,30001</t>
+  </si>
+  <si>
+    <t>10001,20001,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20001,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20001,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20001,30001</t>
+  </si>
+  <si>
+    <t>10001,20002,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20002,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20002,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20002,30001</t>
+  </si>
+  <si>
+    <t>10001,20003,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20003,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20003,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20003,30001</t>
+  </si>
+  <si>
+    <t>10001,20004,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20004,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20004,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20004,30001</t>
+  </si>
+  <si>
+    <t>10001,20005,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20005,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20005,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20005,30001</t>
+  </si>
+  <si>
     <t>10001,20000,30001,40001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,20000,30001,40002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10003,20000,30001,40003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10004,20000,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20001,30001,40001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,20001,30001,40002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10003,20001,30001,40003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10004,20001,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20002,30001,40001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,20002,30001,40002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10003,20002,30001,40003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10004,20002,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10004,20004,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20004,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20004,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20004,30001,40003</t>
-  </si>
-  <si>
-    <t>10001,20003,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20003,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20003,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20003,30001</t>
-  </si>
-  <si>
-    <t>10001,20005,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20005,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20005,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20005,30001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -248,12 +358,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.149998474074526"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -261,26 +557,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -329,7 +915,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -364,7 +950,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -538,186 +1124,181 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I52"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.625" customWidth="1"/>
+    <col min="2" max="2" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+    <col min="4" max="4" width="16.75" customWidth="1"/>
+    <col min="5" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="18.75" customWidth="1"/>
+    <col min="9" max="9" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>10001</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>1000</v>
+      <c r="F5" s="2">
+        <v>10000</v>
       </c>
       <c r="H5" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>10002</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>8</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>2000</v>
+      <c r="F6" s="2">
+        <v>5000</v>
       </c>
       <c r="H6" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>10003</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>12</v>
+      <c r="C7" s="2">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2">
+        <v>10</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -728,21 +1309,21 @@
       <c r="H7" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>10004</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="2">
+        <v>11</v>
+      </c>
+      <c r="D8" s="2">
         <v>12</v>
       </c>
       <c r="E8">
@@ -754,11 +1335,11 @@
       <c r="H8" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>10005</v>
       </c>
@@ -780,11 +1361,11 @@
       <c r="H9" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>10006</v>
       </c>
@@ -806,11 +1387,11 @@
       <c r="H10" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>10007</v>
       </c>
@@ -832,11 +1413,11 @@
       <c r="H11" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>10008</v>
       </c>
@@ -858,11 +1439,11 @@
       <c r="H12" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>10009</v>
       </c>
@@ -884,11 +1465,11 @@
       <c r="H13" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>10010</v>
       </c>
@@ -910,11 +1491,11 @@
       <c r="H14" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>10011</v>
       </c>
@@ -936,11 +1517,11 @@
       <c r="H15" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>10012</v>
       </c>
@@ -962,11 +1543,11 @@
       <c r="H16" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>10013</v>
       </c>
@@ -988,11 +1569,11 @@
       <c r="H17" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I17" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>10014</v>
       </c>
@@ -1014,11 +1595,11 @@
       <c r="H18" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I18" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>10015</v>
       </c>
@@ -1040,11 +1621,11 @@
       <c r="H19" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I19" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>10016</v>
       </c>
@@ -1066,11 +1647,11 @@
       <c r="H20" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I20" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>10017</v>
       </c>
@@ -1092,11 +1673,11 @@
       <c r="H21" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I21" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>10018</v>
       </c>
@@ -1118,11 +1699,11 @@
       <c r="H22" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I22" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>10019</v>
       </c>
@@ -1144,11 +1725,11 @@
       <c r="H23" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I23" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>10020</v>
       </c>
@@ -1170,11 +1751,11 @@
       <c r="H24" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I24" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>10021</v>
       </c>
@@ -1196,11 +1777,11 @@
       <c r="H25" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>10022</v>
       </c>
@@ -1222,11 +1803,11 @@
       <c r="H26" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>10023</v>
       </c>
@@ -1248,11 +1829,11 @@
       <c r="H27" t="s">
         <v>23</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9">
       <c r="A28">
         <v>10024</v>
       </c>
@@ -1274,11 +1855,11 @@
       <c r="H28" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I28" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9">
       <c r="A29">
         <v>20001</v>
       </c>
@@ -1300,11 +1881,11 @@
       <c r="H29" t="s">
         <v>23</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I29" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>20002</v>
       </c>
@@ -1326,11 +1907,11 @@
       <c r="H30" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="I30" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9">
       <c r="A31">
         <v>20003</v>
       </c>
@@ -1352,11 +1933,11 @@
       <c r="H31" t="s">
         <v>23</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9">
       <c r="A32">
         <v>20004</v>
       </c>
@@ -1378,11 +1959,11 @@
       <c r="H32" t="s">
         <v>23</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9">
       <c r="A33">
         <v>20005</v>
       </c>
@@ -1404,11 +1985,11 @@
       <c r="H33" t="s">
         <v>23</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9">
       <c r="A34">
         <v>20006</v>
       </c>
@@ -1430,11 +2011,11 @@
       <c r="H34" t="s">
         <v>23</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35">
         <v>20007</v>
       </c>
@@ -1456,11 +2037,11 @@
       <c r="H35" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9">
       <c r="A36">
         <v>20008</v>
       </c>
@@ -1482,11 +2063,11 @@
       <c r="H36" t="s">
         <v>23</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="I36" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9">
       <c r="A37">
         <v>20009</v>
       </c>
@@ -1508,11 +2089,11 @@
       <c r="H37" t="s">
         <v>23</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="I37" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9">
       <c r="A38">
         <v>20010</v>
       </c>
@@ -1534,11 +2115,11 @@
       <c r="H38" t="s">
         <v>23</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="I38" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9">
       <c r="A39">
         <v>20011</v>
       </c>
@@ -1560,11 +2141,11 @@
       <c r="H39" t="s">
         <v>23</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9">
       <c r="A40">
         <v>20012</v>
       </c>
@@ -1586,11 +2167,11 @@
       <c r="H40" t="s">
         <v>23</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="I40" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9">
       <c r="A41">
         <v>20013</v>
       </c>
@@ -1612,11 +2193,11 @@
       <c r="H41" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I41" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42">
         <v>20014</v>
       </c>
@@ -1638,11 +2219,11 @@
       <c r="H42" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I42" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43">
         <v>20015</v>
       </c>
@@ -1664,11 +2245,11 @@
       <c r="H43" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I43" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44">
         <v>20016</v>
       </c>
@@ -1690,11 +2271,11 @@
       <c r="H44" t="s">
         <v>23</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I44" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45">
         <v>20017</v>
       </c>
@@ -1716,11 +2297,11 @@
       <c r="H45" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I45" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46">
         <v>20018</v>
       </c>
@@ -1742,11 +2323,11 @@
       <c r="H46" t="s">
         <v>23</v>
       </c>
-      <c r="I46" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I46" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47">
         <v>20019</v>
       </c>
@@ -1768,11 +2349,11 @@
       <c r="H47" t="s">
         <v>23</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I47" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48">
         <v>20020</v>
       </c>
@@ -1794,11 +2375,11 @@
       <c r="H48" t="s">
         <v>23</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I48" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49">
         <v>20021</v>
       </c>
@@ -1820,11 +2401,11 @@
       <c r="H49" t="s">
         <v>23</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="I49" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9">
       <c r="A50">
         <v>20022</v>
       </c>
@@ -1846,11 +2427,11 @@
       <c r="H50" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="2" t="s">
+      <c r="I50" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9">
       <c r="A51">
         <v>20023</v>
       </c>
@@ -1872,11 +2453,11 @@
       <c r="H51" t="s">
         <v>23</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="I51" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9">
       <c r="A52">
         <v>20024</v>
       </c>
@@ -1898,12 +2479,12 @@
       <c r="H52" t="s">
         <v>23</v>
       </c>
-      <c r="I52" s="2" t="s">
+      <c r="I52" s="6" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="52">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -107,6 +107,78 @@
     <t>20000,30001</t>
   </si>
   <si>
+    <t>10002,20010,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20010,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20010,30001</t>
+  </si>
+  <si>
+    <t>10001,20001,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20001,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20001,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20001,30001</t>
+  </si>
+  <si>
+    <t>10001,20002,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20002,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20002,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20002,30001</t>
+  </si>
+  <si>
+    <t>10001,20003,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20003,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20003,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20003,30001</t>
+  </si>
+  <si>
+    <t>10001,20004,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20004,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20004,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20004,30001</t>
+  </si>
+  <si>
+    <t>10001,20005,30001,40001</t>
+  </si>
+  <si>
+    <t>10002,20005,30001,40002</t>
+  </si>
+  <si>
+    <t>10003,20005,30001,40003</t>
+  </si>
+  <si>
+    <t>10004,20005,30001</t>
+  </si>
+  <si>
+    <t>10001,20000,30001,40001</t>
+  </si>
+  <si>
     <t>10002,20000,30001,40002</t>
   </si>
   <si>
@@ -114,69 +186,6 @@
   </si>
   <si>
     <t>10004,20000,30001</t>
-  </si>
-  <si>
-    <t>10001,20001,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20001,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20001,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20001,30001</t>
-  </si>
-  <si>
-    <t>10001,20002,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20002,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20002,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20002,30001</t>
-  </si>
-  <si>
-    <t>10001,20003,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20003,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20003,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20003,30001</t>
-  </si>
-  <si>
-    <t>10001,20004,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20004,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20004,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20004,30001</t>
-  </si>
-  <si>
-    <t>10001,20005,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20005,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20005,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20005,30001</t>
-  </si>
-  <si>
-    <t>10001,20000,30001,40001</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1292,7 @@
       <c r="H6" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1309,7 +1318,7 @@
       <c r="H7" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1335,7 +1344,7 @@
       <c r="H8" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1908,7 +1917,7 @@
         <v>23</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1934,7 +1943,7 @@
         <v>23</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1960,7 +1969,7 @@
         <v>23</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:9">

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -107,7 +107,7 @@
     <t>20000,30001</t>
   </si>
   <si>
-    <t>10002,20010,30001,40002</t>
+    <t>10001,20010,30001,40001</t>
   </si>
   <si>
     <t>10003,20010,30001,40003</t>
@@ -812,9 +812,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1266,7 +1267,7 @@
       <c r="H5" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1281,18 +1282,18 @@
         <v>3</v>
       </c>
       <c r="D6" s="2">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H6" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1303,22 +1304,22 @@
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="2">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2">
-        <v>10</v>
+      <c r="C7" s="3">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>36</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>4000</v>
+      <c r="F7" s="2">
+        <v>10000</v>
       </c>
       <c r="H7" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1329,22 +1330,22 @@
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="2">
-        <v>11</v>
-      </c>
-      <c r="D8" s="2">
-        <v>12</v>
+      <c r="C8" s="3">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>36</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>10000</v>
       </c>
       <c r="H8" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="6" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1355,11 +1356,11 @@
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9">
-        <v>13</v>
-      </c>
-      <c r="D9">
-        <v>24</v>
+      <c r="C9" s="3">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>36</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1370,7 +1371,7 @@
       <c r="H9" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1381,11 +1382,11 @@
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10">
-        <v>13</v>
-      </c>
-      <c r="D10">
-        <v>24</v>
+      <c r="C10" s="3">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>36</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1396,7 +1397,7 @@
       <c r="H10" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1407,11 +1408,11 @@
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11">
-        <v>13</v>
-      </c>
-      <c r="D11">
-        <v>24</v>
+      <c r="C11" s="3">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>36</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1422,7 +1423,7 @@
       <c r="H11" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="7" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1433,11 +1434,11 @@
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12">
-        <v>13</v>
-      </c>
-      <c r="D12">
-        <v>24</v>
+      <c r="C12" s="3">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>36</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1448,7 +1449,7 @@
       <c r="H12" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1474,7 +1475,7 @@
       <c r="H13" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="7" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1500,7 +1501,7 @@
       <c r="H14" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1526,7 +1527,7 @@
       <c r="H15" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="7" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1552,7 +1553,7 @@
       <c r="H16" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="7" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1578,7 +1579,7 @@
       <c r="H17" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="7" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1604,7 +1605,7 @@
       <c r="H18" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="7" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1630,7 +1631,7 @@
       <c r="H19" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1656,7 +1657,7 @@
       <c r="H20" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="7" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1682,7 +1683,7 @@
       <c r="H21" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="7" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1708,7 +1709,7 @@
       <c r="H22" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="7" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1734,7 +1735,7 @@
       <c r="H23" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="7" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1760,7 +1761,7 @@
       <c r="H24" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="7" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1786,7 +1787,7 @@
       <c r="H25" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="7" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1812,7 +1813,7 @@
       <c r="H26" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="7" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1838,7 +1839,7 @@
       <c r="H27" t="s">
         <v>23</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="7" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1864,7 +1865,7 @@
       <c r="H28" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1890,7 +1891,7 @@
       <c r="H29" t="s">
         <v>23</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="7" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1916,7 +1917,7 @@
       <c r="H30" t="s">
         <v>23</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1942,7 +1943,7 @@
       <c r="H31" t="s">
         <v>23</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="7" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1968,7 +1969,7 @@
       <c r="H32" t="s">
         <v>23</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="7" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1994,7 +1995,7 @@
       <c r="H33" t="s">
         <v>23</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2020,7 +2021,7 @@
       <c r="H34" t="s">
         <v>23</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="7" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2046,7 +2047,7 @@
       <c r="H35" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="7" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2072,7 +2073,7 @@
       <c r="H36" t="s">
         <v>23</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="I36" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2098,7 +2099,7 @@
       <c r="H37" t="s">
         <v>23</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I37" s="7" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2124,7 +2125,7 @@
       <c r="H38" t="s">
         <v>23</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="I38" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2150,7 +2151,7 @@
       <c r="H39" t="s">
         <v>23</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="7" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2176,7 +2177,7 @@
       <c r="H40" t="s">
         <v>23</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="7" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2202,7 +2203,7 @@
       <c r="H41" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="7" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2228,7 +2229,7 @@
       <c r="H42" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I42" s="7" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2254,7 +2255,7 @@
       <c r="H43" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I43" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2280,7 +2281,7 @@
       <c r="H44" t="s">
         <v>23</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="I44" s="7" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2306,7 +2307,7 @@
       <c r="H45" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="6" t="s">
+      <c r="I45" s="7" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2332,7 +2333,7 @@
       <c r="H46" t="s">
         <v>23</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="I46" s="7" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2358,7 +2359,7 @@
       <c r="H47" t="s">
         <v>23</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="I47" s="7" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2384,7 +2385,7 @@
       <c r="H48" t="s">
         <v>23</v>
       </c>
-      <c r="I48" s="6" t="s">
+      <c r="I48" s="7" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2410,7 +2411,7 @@
       <c r="H49" t="s">
         <v>23</v>
       </c>
-      <c r="I49" s="6" t="s">
+      <c r="I49" s="7" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2436,7 +2437,7 @@
       <c r="H50" t="s">
         <v>23</v>
       </c>
-      <c r="I50" s="6" t="s">
+      <c r="I50" s="7" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2462,7 +2463,7 @@
       <c r="H51" t="s">
         <v>23</v>
       </c>
-      <c r="I51" s="6" t="s">
+      <c r="I51" s="7" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2488,7 +2489,7 @@
       <c r="H52" t="s">
         <v>23</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I52" s="7" t="s">
         <v>47</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E322F9-51EF-48B2-AF3E-5020D6900AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5530B037-27B3-441B-8EB1-452B72CC6FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -692,7 +692,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I5" t="s">
         <v>23</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I6" t="s">
         <v>23</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I7" t="s">
         <v>23</v>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I9" t="s">
         <v>23</v>
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I10" t="s">
         <v>23</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I11" t="s">
         <v>23</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I13" t="s">
         <v>23</v>
@@ -953,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I14" t="s">
         <v>23</v>
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I15" t="s">
         <v>23</v>
@@ -1040,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I17" t="s">
         <v>23</v>
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I18" t="s">
         <v>23</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I19" t="s">
         <v>23</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I21" t="s">
         <v>23</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I22" t="s">
         <v>23</v>
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I23" t="s">
         <v>23</v>
@@ -1272,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I25" t="s">
         <v>23</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I26" t="s">
         <v>23</v>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I27" t="s">
         <v>23</v>
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I29" t="s">
         <v>23</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I30" t="s">
         <v>23</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I31" t="s">
         <v>23</v>
@@ -1504,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I33" t="s">
         <v>23</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I34" t="s">
         <v>23</v>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I35" t="s">
         <v>23</v>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I37" t="s">
         <v>23</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I38" t="s">
         <v>23</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I39" t="s">
         <v>23</v>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I41" t="s">
         <v>23</v>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I42" t="s">
         <v>23</v>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I43" t="s">
         <v>23</v>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I45" t="s">
         <v>23</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I46" t="s">
         <v>23</v>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I47" t="s">
         <v>23</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I49" t="s">
         <v>23</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="I50" t="s">
         <v>23</v>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="I51" t="s">
         <v>23</v>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5530B037-27B3-441B-8EB1-452B72CC6FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229BCCB4-8134-4509-8DFE-55ED6A4AA320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -83,10 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>INT_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>in_barries_kill_min</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -103,10 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MAP&lt;INT:LONG&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>drop_ratio_min</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -127,10 +119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LIST&lt;INT&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>48300001:1</t>
   </si>
   <si>
@@ -224,6 +212,18 @@
   </si>
   <si>
     <t>掉落cd（毫秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_C_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:LONG&gt;_C_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_C_S</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -581,31 +581,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -613,31 +613,31 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -648,7 +648,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -663,7 +663,7 @@
         <v>7</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
@@ -695,10 +695,10 @@
         <v>1500</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -724,10 +724,10 @@
         <v>3000</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -753,10 +753,10 @@
         <v>6000</v>
       </c>
       <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -782,10 +782,10 @@
         <v>10000</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -811,10 +811,10 @@
         <v>1500</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -840,10 +840,10 @@
         <v>3000</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -869,10 +869,10 @@
         <v>6000</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -898,10 +898,10 @@
         <v>10000</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -927,10 +927,10 @@
         <v>1500</v>
       </c>
       <c r="I13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -956,10 +956,10 @@
         <v>3000</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -985,10 +985,10 @@
         <v>6000</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1014,10 +1014,10 @@
         <v>10000</v>
       </c>
       <c r="I16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -1043,10 +1043,10 @@
         <v>1500</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1072,10 +1072,10 @@
         <v>3000</v>
       </c>
       <c r="I18" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -1101,10 +1101,10 @@
         <v>6000</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1130,10 +1130,10 @@
         <v>10000</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -1159,10 +1159,10 @@
         <v>1500</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -1188,10 +1188,10 @@
         <v>3000</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -1217,10 +1217,10 @@
         <v>6000</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1246,10 +1246,10 @@
         <v>10000</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -1275,10 +1275,10 @@
         <v>1500</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -1304,10 +1304,10 @@
         <v>3000</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1333,10 +1333,10 @@
         <v>6000</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1362,10 +1362,10 @@
         <v>10000</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -1391,10 +1391,10 @@
         <v>1500</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -1420,10 +1420,10 @@
         <v>3000</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -1449,10 +1449,10 @@
         <v>6000</v>
       </c>
       <c r="I31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -1478,10 +1478,10 @@
         <v>10000</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -1507,10 +1507,10 @@
         <v>1500</v>
       </c>
       <c r="I33" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -1536,10 +1536,10 @@
         <v>3000</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -1565,10 +1565,10 @@
         <v>6000</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -1594,10 +1594,10 @@
         <v>10000</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -1623,10 +1623,10 @@
         <v>1500</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -1652,10 +1652,10 @@
         <v>3000</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -1681,10 +1681,10 @@
         <v>6000</v>
       </c>
       <c r="I39" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
@@ -1710,10 +1710,10 @@
         <v>10000</v>
       </c>
       <c r="I40" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
@@ -1739,10 +1739,10 @@
         <v>1500</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -1768,10 +1768,10 @@
         <v>3000</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -1797,10 +1797,10 @@
         <v>6000</v>
       </c>
       <c r="I43" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -1826,10 +1826,10 @@
         <v>10000</v>
       </c>
       <c r="I44" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
@@ -1855,10 +1855,10 @@
         <v>1500</v>
       </c>
       <c r="I45" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -1884,10 +1884,10 @@
         <v>3000</v>
       </c>
       <c r="I46" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -1913,10 +1913,10 @@
         <v>6000</v>
       </c>
       <c r="I47" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
@@ -1942,10 +1942,10 @@
         <v>10000</v>
       </c>
       <c r="I48" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
@@ -1971,10 +1971,10 @@
         <v>1500</v>
       </c>
       <c r="I49" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
@@ -2000,10 +2000,10 @@
         <v>3000</v>
       </c>
       <c r="I50" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
@@ -2029,10 +2029,10 @@
         <v>6000</v>
       </c>
       <c r="I51" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
@@ -2058,10 +2058,10 @@
         <v>10000</v>
       </c>
       <c r="I52" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229BCCB4-8134-4509-8DFE-55ED6A4AA320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4888DC3-DD0C-4AA0-B1CA-50144385E6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -122,91 +122,6 @@
     <t>48300001:1</t>
   </si>
   <si>
-    <t>10001,20000,30001,40001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,20000,30001,40002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10003,20000,30001,40003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10004,20000,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20001,30001,40001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,20001,30001,40002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10003,20001,30001,40003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10004,20001,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20002,30001,40001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002,20002,30001,40002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10003,20002,30001,40003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10004,20002,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10004,20004,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20004,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20004,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20004,30001,40003</t>
-  </si>
-  <si>
-    <t>10001,20003,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20003,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20003,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20003,30001</t>
-  </si>
-  <si>
-    <t>10001,20005,30001,40001</t>
-  </si>
-  <si>
-    <t>10002,20005,30001,40002</t>
-  </si>
-  <si>
-    <t>10003,20005,30001,40003</t>
-  </si>
-  <si>
-    <t>10004,20005,30001</t>
-  </si>
-  <si>
     <t>drop_cd</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -225,6 +140,78 @@
   <si>
     <t>LIST&lt;INT&gt;_C_S</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20000,40001</t>
+  </si>
+  <si>
+    <t>10002,20000,40002</t>
+  </si>
+  <si>
+    <t>10003,20000,40003</t>
+  </si>
+  <si>
+    <t>10004,20000</t>
+  </si>
+  <si>
+    <t>10001,20001,40001</t>
+  </si>
+  <si>
+    <t>10002,20001,40002</t>
+  </si>
+  <si>
+    <t>10003,20001,40003</t>
+  </si>
+  <si>
+    <t>10004,20001</t>
+  </si>
+  <si>
+    <t>10001,20002,40001</t>
+  </si>
+  <si>
+    <t>10002,20002,40002</t>
+  </si>
+  <si>
+    <t>10003,20002,40003</t>
+  </si>
+  <si>
+    <t>10004,20002</t>
+  </si>
+  <si>
+    <t>10001,20003,40001</t>
+  </si>
+  <si>
+    <t>10002,20003,40002</t>
+  </si>
+  <si>
+    <t>10003,20003,40003</t>
+  </si>
+  <si>
+    <t>10004,20003</t>
+  </si>
+  <si>
+    <t>10001,20004,40001</t>
+  </si>
+  <si>
+    <t>10002,20004,40002</t>
+  </si>
+  <si>
+    <t>10003,20004,40003</t>
+  </si>
+  <si>
+    <t>10004,20004</t>
+  </si>
+  <si>
+    <t>10001,20005,40001</t>
+  </si>
+  <si>
+    <t>10002,20005,40002</t>
+  </si>
+  <si>
+    <t>10003,20005,40003</t>
+  </si>
+  <si>
+    <t>10004,20005</t>
   </si>
 </sst>
 </file>
@@ -581,31 +568,31 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -616,7 +603,7 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -648,7 +635,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
@@ -698,7 +685,7 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -727,7 +714,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -756,7 +743,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -785,7 +772,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -814,7 +801,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -843,7 +830,7 @@
         <v>20</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -872,7 +859,7 @@
         <v>20</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -901,7 +888,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -930,7 +917,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -959,7 +946,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -988,7 +975,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1017,7 +1004,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -1046,7 +1033,7 @@
         <v>20</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1075,7 +1062,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -1104,7 +1091,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1133,7 +1120,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -1162,7 +1149,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -1191,7 +1178,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -1220,7 +1207,7 @@
         <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1249,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -1278,7 +1265,7 @@
         <v>20</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -1307,7 +1294,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1336,7 +1323,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1365,7 +1352,7 @@
         <v>20</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -1394,7 +1381,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
@@ -1423,7 +1410,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
@@ -1452,7 +1439,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
@@ -1481,7 +1468,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -1510,7 +1497,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -1539,7 +1526,7 @@
         <v>20</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -1568,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -1597,7 +1584,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -1626,7 +1613,7 @@
         <v>20</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -1655,7 +1642,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -1684,7 +1671,7 @@
         <v>20</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
@@ -1713,7 +1700,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
@@ -1742,7 +1729,7 @@
         <v>20</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -1771,7 +1758,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -1800,7 +1787,7 @@
         <v>20</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -1829,7 +1816,7 @@
         <v>20</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
@@ -1858,7 +1845,7 @@
         <v>20</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -1887,7 +1874,7 @@
         <v>20</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -1916,7 +1903,7 @@
         <v>20</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
@@ -1945,7 +1932,7 @@
         <v>20</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
@@ -1974,7 +1961,7 @@
         <v>20</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
@@ -2003,7 +1990,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
@@ -2032,7 +2019,7 @@
         <v>20</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
@@ -2061,7 +2048,7 @@
         <v>20</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4888DC3-DD0C-4AA0-B1CA-50144385E6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C30C0F-0F81-4733-BE36-ED8A3AD65E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -667,13 +667,13 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -696,13 +696,13 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -725,13 +725,13 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -754,13 +754,13 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -783,13 +783,13 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -812,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -841,13 +841,13 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -870,13 +870,13 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D12">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E13">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E14">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -957,13 +957,13 @@
         <v>1</v>
       </c>
       <c r="C15">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E15">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -986,13 +986,13 @@
         <v>1</v>
       </c>
       <c r="C16">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E16">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>1</v>
       </c>
       <c r="C17">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D17">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E17">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         <v>1</v>
       </c>
       <c r="C18">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D18">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E18">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1073,13 +1073,13 @@
         <v>1</v>
       </c>
       <c r="C19">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D19">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E19">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1102,13 +1102,13 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D20">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E20">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="C21">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D21">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E21">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1160,13 +1160,13 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D22">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E22">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="C23">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D23">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E23">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1218,13 +1218,13 @@
         <v>1</v>
       </c>
       <c r="C24">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D24">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E24">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1247,10 +1247,10 @@
         <v>1</v>
       </c>
       <c r="C25">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D25">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E25">
         <v>330</v>
@@ -1276,10 +1276,10 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D26">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E26">
         <v>330</v>
@@ -1305,10 +1305,10 @@
         <v>1</v>
       </c>
       <c r="C27">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D27">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E27">
         <v>330</v>
@@ -1334,10 +1334,10 @@
         <v>1</v>
       </c>
       <c r="C28">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D28">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E28">
         <v>330</v>
@@ -1363,7 +1363,7 @@
         <v>2</v>
       </c>
       <c r="C29">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D29">
         <v>331</v>
@@ -1392,7 +1392,7 @@
         <v>2</v>
       </c>
       <c r="C30">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D30">
         <v>331</v>
@@ -1421,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="C31">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D31">
         <v>331</v>
@@ -1450,7 +1450,7 @@
         <v>2</v>
       </c>
       <c r="C32">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D32">
         <v>331</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="C33">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D33">
         <v>361</v>
@@ -1508,7 +1508,7 @@
         <v>2</v>
       </c>
       <c r="C34">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D34">
         <v>361</v>
@@ -1537,7 +1537,7 @@
         <v>2</v>
       </c>
       <c r="C35">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D35">
         <v>361</v>
@@ -1566,7 +1566,7 @@
         <v>2</v>
       </c>
       <c r="C36">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D36">
         <v>361</v>
@@ -1595,7 +1595,7 @@
         <v>2</v>
       </c>
       <c r="C37">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D37">
         <v>401</v>
@@ -1624,7 +1624,7 @@
         <v>2</v>
       </c>
       <c r="C38">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D38">
         <v>401</v>
@@ -1653,7 +1653,7 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D39">
         <v>401</v>
@@ -1682,7 +1682,7 @@
         <v>2</v>
       </c>
       <c r="C40">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D40">
         <v>401</v>
@@ -1711,7 +1711,7 @@
         <v>2</v>
       </c>
       <c r="C41">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D41">
         <v>451</v>
@@ -1740,7 +1740,7 @@
         <v>2</v>
       </c>
       <c r="C42">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D42">
         <v>451</v>
@@ -1769,7 +1769,7 @@
         <v>2</v>
       </c>
       <c r="C43">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D43">
         <v>451</v>
@@ -1798,7 +1798,7 @@
         <v>2</v>
       </c>
       <c r="C44">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D44">
         <v>451</v>
@@ -1827,7 +1827,7 @@
         <v>2</v>
       </c>
       <c r="C45">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D45">
         <v>501</v>
@@ -1856,7 +1856,7 @@
         <v>2</v>
       </c>
       <c r="C46">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D46">
         <v>501</v>
@@ -1885,7 +1885,7 @@
         <v>2</v>
       </c>
       <c r="C47">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D47">
         <v>501</v>
@@ -1914,7 +1914,7 @@
         <v>2</v>
       </c>
       <c r="C48">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D48">
         <v>501</v>
@@ -1943,7 +1943,7 @@
         <v>2</v>
       </c>
       <c r="C49">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D49">
         <v>551</v>
@@ -1972,7 +1972,7 @@
         <v>2</v>
       </c>
       <c r="C50">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D50">
         <v>551</v>
@@ -2001,7 +2001,7 @@
         <v>2</v>
       </c>
       <c r="C51">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D51">
         <v>501</v>
@@ -2030,7 +2030,7 @@
         <v>2</v>
       </c>
       <c r="C52">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="D52">
         <v>551</v>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C30C0F-0F81-4733-BE36-ED8A3AD65E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF28AA6-3A8E-42DE-9C69-FED6505453E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="51">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -212,6 +212,10 @@
   </si>
   <si>
     <t>10004,20005</t>
+  </si>
+  <si>
+    <t>48300001:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -544,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
@@ -1366,10 +1370,10 @@
         <v>5000</v>
       </c>
       <c r="D29">
-        <v>331</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1395,10 +1399,10 @@
         <v>5000</v>
       </c>
       <c r="D30">
-        <v>331</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1424,10 +1428,10 @@
         <v>5000</v>
       </c>
       <c r="D31">
-        <v>331</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1453,10 +1457,10 @@
         <v>5000</v>
       </c>
       <c r="D32">
-        <v>331</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1482,10 +1486,10 @@
         <v>5000</v>
       </c>
       <c r="D33">
-        <v>361</v>
+        <v>31</v>
       </c>
       <c r="E33">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1511,10 +1515,10 @@
         <v>5000</v>
       </c>
       <c r="D34">
-        <v>361</v>
+        <v>31</v>
       </c>
       <c r="E34">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1540,10 +1544,10 @@
         <v>5000</v>
       </c>
       <c r="D35">
-        <v>361</v>
+        <v>31</v>
       </c>
       <c r="E35">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1552,7 +1556,7 @@
         <v>6000</v>
       </c>
       <c r="I35" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>32</v>
@@ -1569,10 +1573,10 @@
         <v>5000</v>
       </c>
       <c r="D36">
-        <v>361</v>
+        <v>31</v>
       </c>
       <c r="E36">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1598,10 +1602,10 @@
         <v>5000</v>
       </c>
       <c r="D37">
-        <v>401</v>
+        <v>71</v>
       </c>
       <c r="E37">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1627,10 +1631,10 @@
         <v>5000</v>
       </c>
       <c r="D38">
-        <v>401</v>
+        <v>71</v>
       </c>
       <c r="E38">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1656,10 +1660,10 @@
         <v>5000</v>
       </c>
       <c r="D39">
-        <v>401</v>
+        <v>71</v>
       </c>
       <c r="E39">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -1685,10 +1689,10 @@
         <v>5000</v>
       </c>
       <c r="D40">
-        <v>401</v>
+        <v>71</v>
       </c>
       <c r="E40">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -1714,10 +1718,10 @@
         <v>5000</v>
       </c>
       <c r="D41">
-        <v>451</v>
+        <v>121</v>
       </c>
       <c r="E41">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1743,10 +1747,10 @@
         <v>5000</v>
       </c>
       <c r="D42">
-        <v>451</v>
+        <v>121</v>
       </c>
       <c r="E42">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1772,10 +1776,10 @@
         <v>5000</v>
       </c>
       <c r="D43">
-        <v>451</v>
+        <v>121</v>
       </c>
       <c r="E43">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1801,10 +1805,10 @@
         <v>5000</v>
       </c>
       <c r="D44">
-        <v>451</v>
+        <v>121</v>
       </c>
       <c r="E44">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1830,10 +1834,10 @@
         <v>5000</v>
       </c>
       <c r="D45">
-        <v>501</v>
+        <v>171</v>
       </c>
       <c r="E45">
-        <v>550</v>
+        <v>220</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -1859,10 +1863,10 @@
         <v>5000</v>
       </c>
       <c r="D46">
-        <v>501</v>
+        <v>171</v>
       </c>
       <c r="E46">
-        <v>550</v>
+        <v>220</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -1888,10 +1892,10 @@
         <v>5000</v>
       </c>
       <c r="D47">
-        <v>501</v>
+        <v>171</v>
       </c>
       <c r="E47">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1917,10 +1921,10 @@
         <v>5000</v>
       </c>
       <c r="D48">
-        <v>501</v>
+        <v>171</v>
       </c>
       <c r="E48">
-        <v>550</v>
+        <v>220</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -1946,10 +1950,10 @@
         <v>5000</v>
       </c>
       <c r="D49">
-        <v>551</v>
+        <v>221</v>
       </c>
       <c r="E49">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -1975,10 +1979,10 @@
         <v>5000</v>
       </c>
       <c r="D50">
-        <v>551</v>
+        <v>221</v>
       </c>
       <c r="E50">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2004,10 +2008,10 @@
         <v>5000</v>
       </c>
       <c r="D51">
-        <v>501</v>
+        <v>221</v>
       </c>
       <c r="E51">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2033,10 +2037,10 @@
         <v>5000</v>
       </c>
       <c r="D52">
-        <v>551</v>
+        <v>221</v>
       </c>
       <c r="E52">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2049,6 +2053,644 @@
       </c>
       <c r="J52" s="2" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>110001</v>
+      </c>
+      <c r="B53">
+        <v>11</v>
+      </c>
+      <c r="C53">
+        <v>5000</v>
+      </c>
+      <c r="D53">
+        <v>8</v>
+      </c>
+      <c r="E53">
+        <v>15</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>5000</v>
+      </c>
+      <c r="I53" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>110002</v>
+      </c>
+      <c r="B54">
+        <v>11</v>
+      </c>
+      <c r="C54">
+        <v>5000</v>
+      </c>
+      <c r="D54">
+        <v>16</v>
+      </c>
+      <c r="E54">
+        <v>16</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>10000</v>
+      </c>
+      <c r="I54" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>110003</v>
+      </c>
+      <c r="B55">
+        <v>11</v>
+      </c>
+      <c r="C55">
+        <v>5000</v>
+      </c>
+      <c r="D55">
+        <v>17</v>
+      </c>
+      <c r="E55">
+        <v>27</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>4500</v>
+      </c>
+      <c r="I55" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>110004</v>
+      </c>
+      <c r="B56">
+        <v>11</v>
+      </c>
+      <c r="C56">
+        <v>5000</v>
+      </c>
+      <c r="D56">
+        <v>28</v>
+      </c>
+      <c r="E56">
+        <v>28</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>10000</v>
+      </c>
+      <c r="I56" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>110005</v>
+      </c>
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="C57">
+        <v>5000</v>
+      </c>
+      <c r="D57">
+        <v>29</v>
+      </c>
+      <c r="E57">
+        <v>45</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>4000</v>
+      </c>
+      <c r="I57" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57">
+        <v>20002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>110006</v>
+      </c>
+      <c r="B58">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>5000</v>
+      </c>
+      <c r="D58">
+        <v>46</v>
+      </c>
+      <c r="E58">
+        <v>46</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>10000</v>
+      </c>
+      <c r="I58" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58">
+        <v>20002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>110007</v>
+      </c>
+      <c r="B59">
+        <v>11</v>
+      </c>
+      <c r="C59">
+        <v>5000</v>
+      </c>
+      <c r="D59">
+        <v>47</v>
+      </c>
+      <c r="E59">
+        <v>70</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>3000</v>
+      </c>
+      <c r="I59" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59">
+        <v>20003</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>110008</v>
+      </c>
+      <c r="B60">
+        <v>11</v>
+      </c>
+      <c r="C60">
+        <v>5000</v>
+      </c>
+      <c r="D60">
+        <v>71</v>
+      </c>
+      <c r="E60">
+        <v>71</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>10000</v>
+      </c>
+      <c r="I60" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60">
+        <v>20003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>110009</v>
+      </c>
+      <c r="B61">
+        <v>11</v>
+      </c>
+      <c r="C61">
+        <v>5000</v>
+      </c>
+      <c r="D61">
+        <v>72</v>
+      </c>
+      <c r="E61">
+        <v>110</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>2000</v>
+      </c>
+      <c r="I61" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61">
+        <v>20004</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>110010</v>
+      </c>
+      <c r="B62">
+        <v>11</v>
+      </c>
+      <c r="C62">
+        <v>5000</v>
+      </c>
+      <c r="D62">
+        <v>111</v>
+      </c>
+      <c r="E62">
+        <v>111</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>10000</v>
+      </c>
+      <c r="I62" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62">
+        <v>20004</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>110011</v>
+      </c>
+      <c r="B63">
+        <v>11</v>
+      </c>
+      <c r="C63">
+        <v>5000</v>
+      </c>
+      <c r="D63">
+        <v>112</v>
+      </c>
+      <c r="E63">
+        <v>330</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>1000</v>
+      </c>
+      <c r="I63" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63">
+        <v>20005</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>120001</v>
+      </c>
+      <c r="B64">
+        <v>12</v>
+      </c>
+      <c r="C64">
+        <v>5000</v>
+      </c>
+      <c r="D64">
+        <v>10</v>
+      </c>
+      <c r="E64">
+        <v>35</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>3000</v>
+      </c>
+      <c r="I64" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>120002</v>
+      </c>
+      <c r="B65">
+        <v>12</v>
+      </c>
+      <c r="C65">
+        <v>5000</v>
+      </c>
+      <c r="D65">
+        <v>36</v>
+      </c>
+      <c r="E65">
+        <v>36</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>10000</v>
+      </c>
+      <c r="I65" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>120003</v>
+      </c>
+      <c r="B66">
+        <v>12</v>
+      </c>
+      <c r="C66">
+        <v>5000</v>
+      </c>
+      <c r="D66">
+        <v>37</v>
+      </c>
+      <c r="E66">
+        <v>75</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>2500</v>
+      </c>
+      <c r="I66" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>120004</v>
+      </c>
+      <c r="B67">
+        <v>12</v>
+      </c>
+      <c r="C67">
+        <v>5000</v>
+      </c>
+      <c r="D67">
+        <v>76</v>
+      </c>
+      <c r="E67">
+        <v>76</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>10000</v>
+      </c>
+      <c r="I67" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>120005</v>
+      </c>
+      <c r="B68">
+        <v>12</v>
+      </c>
+      <c r="C68">
+        <v>5000</v>
+      </c>
+      <c r="D68">
+        <v>77</v>
+      </c>
+      <c r="E68">
+        <v>125</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>2000</v>
+      </c>
+      <c r="I68" t="s">
+        <v>20</v>
+      </c>
+      <c r="J68">
+        <v>20002</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>120006</v>
+      </c>
+      <c r="B69">
+        <v>12</v>
+      </c>
+      <c r="C69">
+        <v>5000</v>
+      </c>
+      <c r="D69">
+        <v>126</v>
+      </c>
+      <c r="E69">
+        <v>126</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>10000</v>
+      </c>
+      <c r="I69" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69">
+        <v>20002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>120007</v>
+      </c>
+      <c r="B70">
+        <v>12</v>
+      </c>
+      <c r="C70">
+        <v>5000</v>
+      </c>
+      <c r="D70">
+        <v>127</v>
+      </c>
+      <c r="E70">
+        <v>200</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>1500</v>
+      </c>
+      <c r="I70" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70">
+        <v>20003</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>120008</v>
+      </c>
+      <c r="B71">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>5000</v>
+      </c>
+      <c r="D71">
+        <v>201</v>
+      </c>
+      <c r="E71">
+        <v>201</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>10000</v>
+      </c>
+      <c r="I71" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71">
+        <v>20003</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>120009</v>
+      </c>
+      <c r="B72">
+        <v>12</v>
+      </c>
+      <c r="C72">
+        <v>5000</v>
+      </c>
+      <c r="D72">
+        <v>202</v>
+      </c>
+      <c r="E72">
+        <v>290</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>1000</v>
+      </c>
+      <c r="I72" t="s">
+        <v>20</v>
+      </c>
+      <c r="J72">
+        <v>20004</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>120010</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73">
+        <v>5000</v>
+      </c>
+      <c r="D73">
+        <v>291</v>
+      </c>
+      <c r="E73">
+        <v>291</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>10000</v>
+      </c>
+      <c r="I73" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73">
+        <v>20004</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>120011</v>
+      </c>
+      <c r="B74">
+        <v>12</v>
+      </c>
+      <c r="C74">
+        <v>5000</v>
+      </c>
+      <c r="D74">
+        <v>292</v>
+      </c>
+      <c r="E74">
+        <v>580</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>500</v>
+      </c>
+      <c r="I74" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74">
+        <v>20005</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -1,28 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF28AA6-3A8E-42DE-9C69-FED6505453E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="15600"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_barires_drop_v8!$A$4:$J$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_barires_drop_v8!$A$4:$J$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,111 +30,86 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="50">
   <si>
     <t>paipaiworld_config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_C_S</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:LONG&gt;_C_S</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_C_S</t>
   </si>
   <si>
     <t>order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_id</t>
+  </si>
+  <si>
+    <t>drop_cd</t>
+  </si>
+  <si>
+    <t>in_barries_kill_min</t>
+  </si>
+  <si>
+    <t>in_barries_kill_max</t>
+  </si>
+  <si>
+    <t>drop_ratio_min</t>
+  </si>
+  <si>
+    <t>drop_ratio_max</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>drop_items</t>
+  </si>
+  <si>
+    <t>drop_condition</t>
   </si>
   <si>
     <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落cd（毫秒）</t>
   </si>
   <si>
     <t>杀怪数小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落几率万分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>掉落物品：数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落条件id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_items</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_condition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>48300001:1</t>
   </si>
   <si>
-    <t>drop_cd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉落cd（毫秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_C_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:LONG&gt;_C_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_C_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10001,20000,40001</t>
   </si>
   <si>
@@ -212,33 +180,179 @@
   </si>
   <si>
     <t>10004,20005</t>
-  </si>
-  <si>
-    <t>48300001:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,12 +361,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.149998474074526"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -260,29 +560,323 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -328,7 +922,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -363,7 +957,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -537,133 +1131,128 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J74"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.625" customWidth="1"/>
+    <col min="2" max="2" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="15.25" customWidth="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1"/>
+    <col min="5" max="5" width="16.75" customWidth="1"/>
+    <col min="6" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="12.25" customWidth="1"/>
+    <col min="9" max="9" width="18.75" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J4" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>10001</v>
       </c>
@@ -686,13 +1275,13 @@
         <v>1500</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>10002</v>
       </c>
@@ -715,13 +1304,13 @@
         <v>3000</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>10003</v>
       </c>
@@ -744,13 +1333,13 @@
         <v>6000</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>10004</v>
       </c>
@@ -773,13 +1362,13 @@
         <v>10000</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>10005</v>
       </c>
@@ -802,13 +1391,13 @@
         <v>1500</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>10006</v>
       </c>
@@ -831,13 +1420,13 @@
         <v>3000</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>10007</v>
       </c>
@@ -860,13 +1449,13 @@
         <v>6000</v>
       </c>
       <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10008</v>
       </c>
@@ -889,13 +1478,13 @@
         <v>10000</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>10009</v>
       </c>
@@ -918,13 +1507,13 @@
         <v>1500</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>10010</v>
       </c>
@@ -947,13 +1536,13 @@
         <v>3000</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>10011</v>
       </c>
@@ -976,13 +1565,13 @@
         <v>6000</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>10012</v>
       </c>
@@ -1005,13 +1594,13 @@
         <v>10000</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>10013</v>
       </c>
@@ -1034,13 +1623,13 @@
         <v>1500</v>
       </c>
       <c r="I17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>10014</v>
       </c>
@@ -1063,13 +1652,13 @@
         <v>3000</v>
       </c>
       <c r="I18" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>10015</v>
       </c>
@@ -1092,13 +1681,13 @@
         <v>6000</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>10016</v>
       </c>
@@ -1121,13 +1710,13 @@
         <v>10000</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>10017</v>
       </c>
@@ -1150,13 +1739,13 @@
         <v>1500</v>
       </c>
       <c r="I21" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>10018</v>
       </c>
@@ -1179,13 +1768,13 @@
         <v>3000</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>10019</v>
       </c>
@@ -1208,13 +1797,13 @@
         <v>6000</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>10020</v>
       </c>
@@ -1237,13 +1826,13 @@
         <v>10000</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>10021</v>
       </c>
@@ -1266,13 +1855,13 @@
         <v>1500</v>
       </c>
       <c r="I25" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>10022</v>
       </c>
@@ -1295,13 +1884,13 @@
         <v>3000</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>10023</v>
       </c>
@@ -1324,13 +1913,13 @@
         <v>6000</v>
       </c>
       <c r="I27" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>10024</v>
       </c>
@@ -1353,13 +1942,13 @@
         <v>10000</v>
       </c>
       <c r="I28" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>20001</v>
       </c>
@@ -1382,13 +1971,13 @@
         <v>1500</v>
       </c>
       <c r="I29" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>20002</v>
       </c>
@@ -1411,13 +2000,13 @@
         <v>3000</v>
       </c>
       <c r="I30" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31">
         <v>20003</v>
       </c>
@@ -1440,13 +2029,13 @@
         <v>6000</v>
       </c>
       <c r="I31" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32">
         <v>20004</v>
       </c>
@@ -1469,13 +2058,13 @@
         <v>10000</v>
       </c>
       <c r="I32" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33">
         <v>20005</v>
       </c>
@@ -1498,13 +2087,13 @@
         <v>1500</v>
       </c>
       <c r="I33" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34">
         <v>20006</v>
       </c>
@@ -1527,13 +2116,13 @@
         <v>3000</v>
       </c>
       <c r="I34" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35">
         <v>20007</v>
       </c>
@@ -1556,13 +2145,13 @@
         <v>6000</v>
       </c>
       <c r="I35" t="s">
-        <v>50</v>
-      </c>
-      <c r="J35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36">
         <v>20008</v>
       </c>
@@ -1585,13 +2174,13 @@
         <v>10000</v>
       </c>
       <c r="I36" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37">
         <v>20009</v>
       </c>
@@ -1614,13 +2203,13 @@
         <v>1500</v>
       </c>
       <c r="I37" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38">
         <v>20010</v>
       </c>
@@ -1643,13 +2232,13 @@
         <v>3000</v>
       </c>
       <c r="I38" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10">
       <c r="A39">
         <v>20011</v>
       </c>
@@ -1672,13 +2261,13 @@
         <v>6000</v>
       </c>
       <c r="I39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10">
       <c r="A40">
         <v>20012</v>
       </c>
@@ -1701,13 +2290,13 @@
         <v>10000</v>
       </c>
       <c r="I40" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10">
       <c r="A41">
         <v>20013</v>
       </c>
@@ -1730,13 +2319,13 @@
         <v>1500</v>
       </c>
       <c r="I41" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10">
       <c r="A42">
         <v>20014</v>
       </c>
@@ -1759,13 +2348,13 @@
         <v>3000</v>
       </c>
       <c r="I42" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10">
       <c r="A43">
         <v>20015</v>
       </c>
@@ -1788,13 +2377,13 @@
         <v>6000</v>
       </c>
       <c r="I43" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10">
       <c r="A44">
         <v>20016</v>
       </c>
@@ -1817,13 +2406,13 @@
         <v>10000</v>
       </c>
       <c r="I44" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10">
       <c r="A45">
         <v>20017</v>
       </c>
@@ -1846,13 +2435,13 @@
         <v>1500</v>
       </c>
       <c r="I45" t="s">
-        <v>20</v>
-      </c>
-      <c r="J45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10">
       <c r="A46">
         <v>20018</v>
       </c>
@@ -1875,13 +2464,13 @@
         <v>3000</v>
       </c>
       <c r="I46" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10">
       <c r="A47">
         <v>20019</v>
       </c>
@@ -1904,13 +2493,13 @@
         <v>6000</v>
       </c>
       <c r="I47" t="s">
-        <v>20</v>
-      </c>
-      <c r="J47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10">
       <c r="A48">
         <v>20020</v>
       </c>
@@ -1933,13 +2522,13 @@
         <v>10000</v>
       </c>
       <c r="I48" t="s">
-        <v>20</v>
-      </c>
-      <c r="J48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10">
       <c r="A49">
         <v>20021</v>
       </c>
@@ -1962,13 +2551,13 @@
         <v>1500</v>
       </c>
       <c r="I49" t="s">
-        <v>20</v>
-      </c>
-      <c r="J49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10">
       <c r="A50">
         <v>20022</v>
       </c>
@@ -1991,13 +2580,13 @@
         <v>3000</v>
       </c>
       <c r="I50" t="s">
-        <v>20</v>
-      </c>
-      <c r="J50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10">
       <c r="A51">
         <v>20023</v>
       </c>
@@ -2020,13 +2609,13 @@
         <v>6000</v>
       </c>
       <c r="I51" t="s">
-        <v>20</v>
-      </c>
-      <c r="J51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J51" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10">
       <c r="A52">
         <v>20024</v>
       </c>
@@ -2049,13 +2638,13 @@
         <v>10000</v>
       </c>
       <c r="I52" t="s">
-        <v>20</v>
-      </c>
-      <c r="J52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10">
       <c r="A53">
         <v>110001</v>
       </c>
@@ -2075,16 +2664,16 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J53">
         <v>20000</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10">
       <c r="A54">
         <v>110002</v>
       </c>
@@ -2107,13 +2696,13 @@
         <v>10000</v>
       </c>
       <c r="I54" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J54">
         <v>20000</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10">
       <c r="A55">
         <v>110003</v>
       </c>
@@ -2133,16 +2722,16 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J55">
         <v>20001</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10">
       <c r="A56">
         <v>110004</v>
       </c>
@@ -2165,13 +2754,13 @@
         <v>10000</v>
       </c>
       <c r="I56" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J56">
         <v>20001</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10">
       <c r="A57">
         <v>110005</v>
       </c>
@@ -2191,16 +2780,16 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J57">
         <v>20002</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10">
       <c r="A58">
         <v>110006</v>
       </c>
@@ -2223,13 +2812,13 @@
         <v>10000</v>
       </c>
       <c r="I58" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J58">
         <v>20002</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10">
       <c r="A59">
         <v>110007</v>
       </c>
@@ -2249,16 +2838,16 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J59">
         <v>20003</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10">
       <c r="A60">
         <v>110008</v>
       </c>
@@ -2281,13 +2870,13 @@
         <v>10000</v>
       </c>
       <c r="I60" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J60">
         <v>20003</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10">
       <c r="A61">
         <v>110009</v>
       </c>
@@ -2307,16 +2896,16 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J61">
         <v>20004</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10">
       <c r="A62">
         <v>110010</v>
       </c>
@@ -2339,13 +2928,13 @@
         <v>10000</v>
       </c>
       <c r="I62" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J62">
         <v>20004</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10">
       <c r="A63">
         <v>110011</v>
       </c>
@@ -2365,16 +2954,16 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J63">
         <v>20005</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10">
       <c r="A64">
         <v>120001</v>
       </c>
@@ -2397,13 +2986,13 @@
         <v>3000</v>
       </c>
       <c r="I64" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J64">
         <v>20000</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10">
       <c r="A65">
         <v>120002</v>
       </c>
@@ -2426,13 +3015,13 @@
         <v>10000</v>
       </c>
       <c r="I65" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J65">
         <v>20000</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10">
       <c r="A66">
         <v>120003</v>
       </c>
@@ -2455,13 +3044,13 @@
         <v>2500</v>
       </c>
       <c r="I66" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J66">
         <v>20001</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10">
       <c r="A67">
         <v>120004</v>
       </c>
@@ -2484,13 +3073,13 @@
         <v>10000</v>
       </c>
       <c r="I67" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J67">
         <v>20001</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10">
       <c r="A68">
         <v>120005</v>
       </c>
@@ -2513,13 +3102,13 @@
         <v>2000</v>
       </c>
       <c r="I68" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J68">
         <v>20002</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10">
       <c r="A69">
         <v>120006</v>
       </c>
@@ -2542,13 +3131,13 @@
         <v>10000</v>
       </c>
       <c r="I69" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J69">
         <v>20002</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10">
       <c r="A70">
         <v>120007</v>
       </c>
@@ -2571,13 +3160,13 @@
         <v>1500</v>
       </c>
       <c r="I70" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J70">
         <v>20003</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10">
       <c r="A71">
         <v>120008</v>
       </c>
@@ -2600,13 +3189,13 @@
         <v>10000</v>
       </c>
       <c r="I71" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J71">
         <v>20003</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10">
       <c r="A72">
         <v>120009</v>
       </c>
@@ -2629,13 +3218,13 @@
         <v>1000</v>
       </c>
       <c r="I72" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J72">
         <v>20004</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10">
       <c r="A73">
         <v>120010</v>
       </c>
@@ -2658,13 +3247,13 @@
         <v>10000</v>
       </c>
       <c r="I73" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J73">
         <v>20004</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10">
       <c r="A74">
         <v>120011</v>
       </c>
@@ -2687,14 +3276,14 @@
         <v>500</v>
       </c>
       <c r="I74" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J74">
         <v>20005</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -1,19 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF28AA6-3A8E-42DE-9C69-FED6505453E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15600"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_barires_drop_v8!$A$4:$J$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_barires_drop_v8!$A$4:$J$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -21,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,329 +37,208 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="51">
   <si>
     <t>paipaiworld_config</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>order</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀怪数小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀怪数大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落几率万分比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落物品：数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落条件id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>in_barries_kill_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>in_barries_kill_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_items</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_condition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_ratio_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_ratio_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300001:1</t>
+  </si>
+  <si>
+    <t>drop_cd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落cd（毫秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_C_S</t>
-  </si>
-  <si>
-    <t>STRING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MAP&lt;INT:LONG&gt;_C_S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>LIST&lt;INT&gt;_C_S</t>
-  </si>
-  <si>
-    <t>order</t>
-  </si>
-  <si>
-    <t>drop_id</t>
-  </si>
-  <si>
-    <t>drop_cd</t>
-  </si>
-  <si>
-    <t>in_barries_kill_min</t>
-  </si>
-  <si>
-    <t>in_barries_kill_max</t>
-  </si>
-  <si>
-    <t>drop_ratio_min</t>
-  </si>
-  <si>
-    <t>drop_ratio_max</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>drop_items</t>
-  </si>
-  <si>
-    <t>drop_condition</t>
-  </si>
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>掉落id</t>
-  </si>
-  <si>
-    <t>掉落cd（毫秒）</t>
-  </si>
-  <si>
-    <t>杀怪数小</t>
-  </si>
-  <si>
-    <t>杀怪数大</t>
-  </si>
-  <si>
-    <t>掉落几率万分比</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>掉落物品：数量</t>
-  </si>
-  <si>
-    <t>掉落条件id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20000,40001</t>
+  </si>
+  <si>
+    <t>10002,20000,40002</t>
+  </si>
+  <si>
+    <t>10003,20000,40003</t>
+  </si>
+  <si>
+    <t>10004,20000</t>
+  </si>
+  <si>
+    <t>10001,20001,40001</t>
+  </si>
+  <si>
+    <t>10002,20001,40002</t>
+  </si>
+  <si>
+    <t>10003,20001,40003</t>
+  </si>
+  <si>
+    <t>10004,20001</t>
+  </si>
+  <si>
+    <t>10001,20002,40001</t>
+  </si>
+  <si>
+    <t>10002,20002,40002</t>
+  </si>
+  <si>
+    <t>10003,20002,40003</t>
+  </si>
+  <si>
+    <t>10004,20002</t>
+  </si>
+  <si>
+    <t>10001,20003,40001</t>
+  </si>
+  <si>
+    <t>10002,20003,40002</t>
+  </si>
+  <si>
+    <t>10003,20003,40003</t>
+  </si>
+  <si>
+    <t>10004,20003</t>
+  </si>
+  <si>
+    <t>10001,20004,40001</t>
+  </si>
+  <si>
+    <t>10002,20004,40002</t>
+  </si>
+  <si>
+    <t>10003,20004,40003</t>
+  </si>
+  <si>
+    <t>10004,20004</t>
+  </si>
+  <si>
+    <t>10001,20005,40001</t>
+  </si>
+  <si>
+    <t>10002,20005,40002</t>
+  </si>
+  <si>
+    <t>10003,20005,40003</t>
+  </si>
+  <si>
+    <t>10004,20005</t>
   </si>
   <si>
     <t>48300001:1</t>
-  </si>
-  <si>
-    <t>10001,20000,40001</t>
-  </si>
-  <si>
-    <t>10002,20000,40002</t>
-  </si>
-  <si>
-    <t>10003,20000,40003</t>
-  </si>
-  <si>
-    <t>10004,20000</t>
-  </si>
-  <si>
-    <t>10001,20001,40001</t>
-  </si>
-  <si>
-    <t>10002,20001,40002</t>
-  </si>
-  <si>
-    <t>10003,20001,40003</t>
-  </si>
-  <si>
-    <t>10004,20001</t>
-  </si>
-  <si>
-    <t>10001,20002,40001</t>
-  </si>
-  <si>
-    <t>10002,20002,40002</t>
-  </si>
-  <si>
-    <t>10003,20002,40003</t>
-  </si>
-  <si>
-    <t>10004,20002</t>
-  </si>
-  <si>
-    <t>10001,20003,40001</t>
-  </si>
-  <si>
-    <t>10002,20003,40002</t>
-  </si>
-  <si>
-    <t>10003,20003,40003</t>
-  </si>
-  <si>
-    <t>10004,20003</t>
-  </si>
-  <si>
-    <t>10001,20004,40001</t>
-  </si>
-  <si>
-    <t>10002,20004,40002</t>
-  </si>
-  <si>
-    <t>10003,20004,40003</t>
-  </si>
-  <si>
-    <t>10004,20004</t>
-  </si>
-  <si>
-    <t>10001,20005,40001</t>
-  </si>
-  <si>
-    <t>10002,20005,40002</t>
-  </si>
-  <si>
-    <t>10003,20005,40003</t>
-  </si>
-  <si>
-    <t>10004,20005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,198 +247,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149998474074526"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -560,323 +260,29 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -922,7 +328,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -957,7 +363,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -1131,128 +537,133 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J74"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.625" customWidth="1"/>
-    <col min="2" max="2" width="8.75" customWidth="1"/>
-    <col min="3" max="3" width="15.25" customWidth="1"/>
-    <col min="4" max="4" width="16.25" customWidth="1"/>
-    <col min="5" max="5" width="16.75" customWidth="1"/>
-    <col min="6" max="7" width="17.125" customWidth="1"/>
-    <col min="8" max="8" width="12.25" customWidth="1"/>
-    <col min="9" max="9" width="18.75" customWidth="1"/>
-    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="I2" t="s">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="J2" t="s">
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
+      <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="J4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>10001</v>
       </c>
@@ -1275,13 +686,13 @@
         <v>1500</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>10002</v>
       </c>
@@ -1304,13 +715,13 @@
         <v>3000</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>10003</v>
       </c>
@@ -1333,13 +744,13 @@
         <v>6000</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>10004</v>
       </c>
@@ -1362,13 +773,13 @@
         <v>10000</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>10005</v>
       </c>
@@ -1391,13 +802,13 @@
         <v>1500</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>10006</v>
       </c>
@@ -1420,13 +831,13 @@
         <v>3000</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10007</v>
       </c>
@@ -1449,13 +860,13 @@
         <v>6000</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
-      </c>
-      <c r="J11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10008</v>
       </c>
@@ -1478,13 +889,13 @@
         <v>10000</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>10009</v>
       </c>
@@ -1507,13 +918,13 @@
         <v>1500</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10010</v>
       </c>
@@ -1536,13 +947,13 @@
         <v>3000</v>
       </c>
       <c r="I14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>10011</v>
       </c>
@@ -1565,13 +976,13 @@
         <v>6000</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>10012</v>
       </c>
@@ -1594,13 +1005,13 @@
         <v>10000</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>10013</v>
       </c>
@@ -1623,13 +1034,13 @@
         <v>1500</v>
       </c>
       <c r="I17" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>10014</v>
       </c>
@@ -1652,13 +1063,13 @@
         <v>3000</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>10015</v>
       </c>
@@ -1681,13 +1092,13 @@
         <v>6000</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
-      </c>
-      <c r="J19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>10016</v>
       </c>
@@ -1710,13 +1121,13 @@
         <v>10000</v>
       </c>
       <c r="I20" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>10017</v>
       </c>
@@ -1739,13 +1150,13 @@
         <v>1500</v>
       </c>
       <c r="I21" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>10018</v>
       </c>
@@ -1768,13 +1179,13 @@
         <v>3000</v>
       </c>
       <c r="I22" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>10019</v>
       </c>
@@ -1797,13 +1208,13 @@
         <v>6000</v>
       </c>
       <c r="I23" t="s">
-        <v>25</v>
-      </c>
-      <c r="J23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>10020</v>
       </c>
@@ -1826,13 +1237,13 @@
         <v>10000</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
-      </c>
-      <c r="J24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>10021</v>
       </c>
@@ -1855,13 +1266,13 @@
         <v>1500</v>
       </c>
       <c r="I25" t="s">
-        <v>25</v>
-      </c>
-      <c r="J25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>10022</v>
       </c>
@@ -1884,13 +1295,13 @@
         <v>3000</v>
       </c>
       <c r="I26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>10023</v>
       </c>
@@ -1913,13 +1324,13 @@
         <v>6000</v>
       </c>
       <c r="I27" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>10024</v>
       </c>
@@ -1942,13 +1353,13 @@
         <v>10000</v>
       </c>
       <c r="I28" t="s">
-        <v>25</v>
-      </c>
-      <c r="J28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>20001</v>
       </c>
@@ -1971,13 +1382,13 @@
         <v>1500</v>
       </c>
       <c r="I29" t="s">
-        <v>25</v>
-      </c>
-      <c r="J29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>20002</v>
       </c>
@@ -2000,13 +1411,13 @@
         <v>3000</v>
       </c>
       <c r="I30" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>20003</v>
       </c>
@@ -2029,13 +1440,13 @@
         <v>6000</v>
       </c>
       <c r="I31" t="s">
-        <v>25</v>
-      </c>
-      <c r="J31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>20004</v>
       </c>
@@ -2058,13 +1469,13 @@
         <v>10000</v>
       </c>
       <c r="I32" t="s">
-        <v>25</v>
-      </c>
-      <c r="J32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>20005</v>
       </c>
@@ -2087,13 +1498,13 @@
         <v>1500</v>
       </c>
       <c r="I33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>20006</v>
       </c>
@@ -2116,13 +1527,13 @@
         <v>3000</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
-      </c>
-      <c r="J34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>20007</v>
       </c>
@@ -2145,13 +1556,13 @@
         <v>6000</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
-      </c>
-      <c r="J35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>20008</v>
       </c>
@@ -2174,13 +1585,13 @@
         <v>10000</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
-      </c>
-      <c r="J36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>20009</v>
       </c>
@@ -2203,13 +1614,13 @@
         <v>1500</v>
       </c>
       <c r="I37" t="s">
-        <v>25</v>
-      </c>
-      <c r="J37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>20010</v>
       </c>
@@ -2232,13 +1643,13 @@
         <v>3000</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
-      </c>
-      <c r="J38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>20011</v>
       </c>
@@ -2261,13 +1672,13 @@
         <v>6000</v>
       </c>
       <c r="I39" t="s">
-        <v>25</v>
-      </c>
-      <c r="J39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>20012</v>
       </c>
@@ -2290,13 +1701,13 @@
         <v>10000</v>
       </c>
       <c r="I40" t="s">
-        <v>25</v>
-      </c>
-      <c r="J40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>20013</v>
       </c>
@@ -2319,13 +1730,13 @@
         <v>1500</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
-      </c>
-      <c r="J41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>20014</v>
       </c>
@@ -2348,13 +1759,13 @@
         <v>3000</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
-      </c>
-      <c r="J42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>20015</v>
       </c>
@@ -2377,13 +1788,13 @@
         <v>6000</v>
       </c>
       <c r="I43" t="s">
-        <v>25</v>
-      </c>
-      <c r="J43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>20016</v>
       </c>
@@ -2406,13 +1817,13 @@
         <v>10000</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>20017</v>
       </c>
@@ -2435,13 +1846,13 @@
         <v>1500</v>
       </c>
       <c r="I45" t="s">
-        <v>25</v>
-      </c>
-      <c r="J45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>20018</v>
       </c>
@@ -2464,13 +1875,13 @@
         <v>3000</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
-      </c>
-      <c r="J46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>20019</v>
       </c>
@@ -2493,13 +1904,13 @@
         <v>6000</v>
       </c>
       <c r="I47" t="s">
-        <v>25</v>
-      </c>
-      <c r="J47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>20020</v>
       </c>
@@ -2522,13 +1933,13 @@
         <v>10000</v>
       </c>
       <c r="I48" t="s">
-        <v>25</v>
-      </c>
-      <c r="J48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>20021</v>
       </c>
@@ -2551,13 +1962,13 @@
         <v>1500</v>
       </c>
       <c r="I49" t="s">
-        <v>25</v>
-      </c>
-      <c r="J49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>20022</v>
       </c>
@@ -2580,13 +1991,13 @@
         <v>3000</v>
       </c>
       <c r="I50" t="s">
-        <v>25</v>
-      </c>
-      <c r="J50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>20023</v>
       </c>
@@ -2609,13 +2020,13 @@
         <v>6000</v>
       </c>
       <c r="I51" t="s">
-        <v>25</v>
-      </c>
-      <c r="J51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>20024</v>
       </c>
@@ -2638,13 +2049,13 @@
         <v>10000</v>
       </c>
       <c r="I52" t="s">
-        <v>25</v>
-      </c>
-      <c r="J52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>110001</v>
       </c>
@@ -2664,16 +2075,16 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I53" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J53">
         <v>20000</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>110002</v>
       </c>
@@ -2696,13 +2107,13 @@
         <v>10000</v>
       </c>
       <c r="I54" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J54">
         <v>20000</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>110003</v>
       </c>
@@ -2722,16 +2133,16 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="I55" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J55">
         <v>20001</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>110004</v>
       </c>
@@ -2754,13 +2165,13 @@
         <v>10000</v>
       </c>
       <c r="I56" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J56">
         <v>20001</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>110005</v>
       </c>
@@ -2780,16 +2191,16 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I57" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J57">
         <v>20002</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>110006</v>
       </c>
@@ -2812,13 +2223,13 @@
         <v>10000</v>
       </c>
       <c r="I58" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J58">
         <v>20002</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>110007</v>
       </c>
@@ -2838,16 +2249,16 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I59" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J59">
         <v>20003</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>110008</v>
       </c>
@@ -2870,13 +2281,13 @@
         <v>10000</v>
       </c>
       <c r="I60" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J60">
         <v>20003</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>110009</v>
       </c>
@@ -2896,16 +2307,16 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I61" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J61">
         <v>20004</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>110010</v>
       </c>
@@ -2928,13 +2339,13 @@
         <v>10000</v>
       </c>
       <c r="I62" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J62">
         <v>20004</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>110011</v>
       </c>
@@ -2954,16 +2365,16 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I63" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J63">
         <v>20005</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>120001</v>
       </c>
@@ -2986,13 +2397,13 @@
         <v>3000</v>
       </c>
       <c r="I64" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J64">
         <v>20000</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>120002</v>
       </c>
@@ -3015,13 +2426,13 @@
         <v>10000</v>
       </c>
       <c r="I65" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J65">
         <v>20000</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>120003</v>
       </c>
@@ -3044,13 +2455,13 @@
         <v>2500</v>
       </c>
       <c r="I66" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J66">
         <v>20001</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>120004</v>
       </c>
@@ -3073,13 +2484,13 @@
         <v>10000</v>
       </c>
       <c r="I67" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J67">
         <v>20001</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>120005</v>
       </c>
@@ -3102,13 +2513,13 @@
         <v>2000</v>
       </c>
       <c r="I68" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J68">
         <v>20002</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>120006</v>
       </c>
@@ -3131,13 +2542,13 @@
         <v>10000</v>
       </c>
       <c r="I69" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J69">
         <v>20002</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>120007</v>
       </c>
@@ -3160,13 +2571,13 @@
         <v>1500</v>
       </c>
       <c r="I70" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J70">
         <v>20003</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>120008</v>
       </c>
@@ -3189,13 +2600,13 @@
         <v>10000</v>
       </c>
       <c r="I71" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J71">
         <v>20003</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>120009</v>
       </c>
@@ -3218,13 +2629,13 @@
         <v>1000</v>
       </c>
       <c r="I72" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J72">
         <v>20004</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>120010</v>
       </c>
@@ -3247,13 +2658,13 @@
         <v>10000</v>
       </c>
       <c r="I73" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J73">
         <v>20004</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>120011</v>
       </c>
@@ -3276,14 +2687,14 @@
         <v>500</v>
       </c>
       <c r="I74" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J74">
         <v>20005</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF28AA6-3A8E-42DE-9C69-FED6505453E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C370DA25-0F01-4DF1-82A0-41D02129B1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="51">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -548,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
@@ -2066,10 +2066,10 @@
         <v>5000</v>
       </c>
       <c r="D53">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E53">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2095,10 +2095,10 @@
         <v>5000</v>
       </c>
       <c r="D54">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E54">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2124,16 +2124,16 @@
         <v>5000</v>
       </c>
       <c r="D55">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E55">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="I55" t="s">
         <v>20</v>
@@ -2153,10 +2153,10 @@
         <v>5000</v>
       </c>
       <c r="D56">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E56">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2182,16 +2182,16 @@
         <v>5000</v>
       </c>
       <c r="D57">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E57">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I57" t="s">
         <v>20</v>
@@ -2211,10 +2211,10 @@
         <v>5000</v>
       </c>
       <c r="D58">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="E58">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2240,16 +2240,16 @@
         <v>5000</v>
       </c>
       <c r="D59">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="E59">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I59" t="s">
         <v>20</v>
@@ -2269,10 +2269,10 @@
         <v>5000</v>
       </c>
       <c r="D60">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="E60">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2298,16 +2298,16 @@
         <v>5000</v>
       </c>
       <c r="D61">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="E61">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I61" t="s">
         <v>20</v>
@@ -2318,65 +2318,65 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>110010</v>
+        <v>120001</v>
       </c>
       <c r="B62">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C62">
         <v>5000</v>
       </c>
       <c r="D62">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="E62">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="I62" t="s">
         <v>20</v>
       </c>
       <c r="J62">
-        <v>20004</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>110011</v>
+        <v>120002</v>
       </c>
       <c r="B63">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C63">
         <v>5000</v>
       </c>
       <c r="D63">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="E63">
-        <v>330</v>
+        <v>41</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="I63" t="s">
         <v>20</v>
       </c>
       <c r="J63">
-        <v>20005</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>120001</v>
+        <v>120003</v>
       </c>
       <c r="B64">
         <v>12</v>
@@ -2385,27 +2385,27 @@
         <v>5000</v>
       </c>
       <c r="D64">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E64">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="I64" t="s">
         <v>20</v>
       </c>
       <c r="J64">
-        <v>20000</v>
+        <v>20001</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>120002</v>
+        <v>120004</v>
       </c>
       <c r="B65">
         <v>12</v>
@@ -2414,10 +2414,10 @@
         <v>5000</v>
       </c>
       <c r="D65">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="E65">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -2429,12 +2429,12 @@
         <v>20</v>
       </c>
       <c r="J65">
-        <v>20000</v>
+        <v>20001</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>120003</v>
+        <v>120005</v>
       </c>
       <c r="B66">
         <v>12</v>
@@ -2443,27 +2443,27 @@
         <v>5000</v>
       </c>
       <c r="D66">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="E66">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="I66" t="s">
         <v>20</v>
       </c>
       <c r="J66">
-        <v>20001</v>
+        <v>20002</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>120004</v>
+        <v>120006</v>
       </c>
       <c r="B67">
         <v>12</v>
@@ -2472,10 +2472,10 @@
         <v>5000</v>
       </c>
       <c r="D67">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="E67">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -2487,12 +2487,12 @@
         <v>20</v>
       </c>
       <c r="J67">
-        <v>20001</v>
+        <v>20002</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>120005</v>
+        <v>120007</v>
       </c>
       <c r="B68">
         <v>12</v>
@@ -2501,27 +2501,27 @@
         <v>5000</v>
       </c>
       <c r="D68">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="E68">
-        <v>125</v>
+        <v>310</v>
       </c>
       <c r="F68">
         <v>0</v>
       </c>
       <c r="G68">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="I68" t="s">
         <v>20</v>
       </c>
       <c r="J68">
-        <v>20002</v>
+        <v>20003</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>120006</v>
+        <v>120008</v>
       </c>
       <c r="B69">
         <v>12</v>
@@ -2530,10 +2530,10 @@
         <v>5000</v>
       </c>
       <c r="D69">
-        <v>126</v>
+        <v>311</v>
       </c>
       <c r="E69">
-        <v>126</v>
+        <v>311</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2545,12 +2545,12 @@
         <v>20</v>
       </c>
       <c r="J69">
-        <v>20002</v>
+        <v>20003</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>120007</v>
+        <v>120009</v>
       </c>
       <c r="B70">
         <v>12</v>
@@ -2559,138 +2559,22 @@
         <v>5000</v>
       </c>
       <c r="D70">
-        <v>127</v>
+        <v>312</v>
       </c>
       <c r="E70">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="I70" t="s">
         <v>20</v>
       </c>
       <c r="J70">
-        <v>20003</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>120008</v>
-      </c>
-      <c r="B71">
-        <v>12</v>
-      </c>
-      <c r="C71">
-        <v>5000</v>
-      </c>
-      <c r="D71">
-        <v>201</v>
-      </c>
-      <c r="E71">
-        <v>201</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71">
-        <v>10000</v>
-      </c>
-      <c r="I71" t="s">
-        <v>20</v>
-      </c>
-      <c r="J71">
-        <v>20003</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A72">
-        <v>120009</v>
-      </c>
-      <c r="B72">
-        <v>12</v>
-      </c>
-      <c r="C72">
-        <v>5000</v>
-      </c>
-      <c r="D72">
-        <v>202</v>
-      </c>
-      <c r="E72">
-        <v>290</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="G72">
-        <v>1000</v>
-      </c>
-      <c r="I72" t="s">
-        <v>20</v>
-      </c>
-      <c r="J72">
         <v>20004</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A73">
-        <v>120010</v>
-      </c>
-      <c r="B73">
-        <v>12</v>
-      </c>
-      <c r="C73">
-        <v>5000</v>
-      </c>
-      <c r="D73">
-        <v>291</v>
-      </c>
-      <c r="E73">
-        <v>291</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73">
-        <v>10000</v>
-      </c>
-      <c r="I73" t="s">
-        <v>20</v>
-      </c>
-      <c r="J73">
-        <v>20004</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A74">
-        <v>120011</v>
-      </c>
-      <c r="B74">
-        <v>12</v>
-      </c>
-      <c r="C74">
-        <v>5000</v>
-      </c>
-      <c r="D74">
-        <v>292</v>
-      </c>
-      <c r="E74">
-        <v>580</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <v>500</v>
-      </c>
-      <c r="I74" t="s">
-        <v>20</v>
-      </c>
-      <c r="J74">
-        <v>20005</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C370DA25-0F01-4DF1-82A0-41D02129B1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC450BE5-D33C-44CE-AA28-B065E406F850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="I53" t="s">
         <v>20</v>
@@ -2127,13 +2127,13 @@
         <v>20</v>
       </c>
       <c r="E55">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="I55" t="s">
         <v>20</v>
@@ -2153,10 +2153,10 @@
         <v>5000</v>
       </c>
       <c r="D56">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E56">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2182,16 +2182,16 @@
         <v>5000</v>
       </c>
       <c r="D57">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E57">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F57">
         <v>0</v>
       </c>
       <c r="G57">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I57" t="s">
         <v>20</v>
@@ -2211,10 +2211,10 @@
         <v>5000</v>
       </c>
       <c r="D58">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="E58">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2240,16 +2240,16 @@
         <v>5000</v>
       </c>
       <c r="D59">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E59">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="F59">
         <v>0</v>
       </c>
       <c r="G59">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I59" t="s">
         <v>20</v>
@@ -2269,10 +2269,10 @@
         <v>5000</v>
       </c>
       <c r="D60">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="E60">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2298,7 +2298,7 @@
         <v>5000</v>
       </c>
       <c r="D61">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E61">
         <v>330</v>
@@ -2327,7 +2327,7 @@
         <v>5000</v>
       </c>
       <c r="D62">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E62">
         <v>40</v>
